--- a/tame_output/ON/bt/strategyON_20240606.xlsx
+++ b/tame_output/ON/bt/strategyON_20240606.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-18.5%</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.5%</t>
+          <t>453.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-687.4%</t>
+          <t>-688.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-299.2%</t>
+          <t>-294.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-278.0%</t>
+          <t>-279.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-191.0%</t>
+          <t>-186.2%</t>
         </is>
       </c>
     </row>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.01139285002782</v>
       </c>
       <c r="D1966" t="n">
         <v>-5.272384315089162</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8451878153281163</v>
+        <v>0.9020826996784086</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7100607248039429</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.528461530795163</v>
+        <v>2.585356415145455</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.014186471559301</v>
       </c>
       <c r="D1967" t="n">
         <v>-5.374398997620383</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8071755638471085</v>
+        <v>0.8640704481974009</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7100607248039429</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.531255152326644</v>
+        <v>2.588150036676936</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.01484881995096</v>
       </c>
       <c r="D1968" t="n">
         <v>-5.23778965352629</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8624816498764041</v>
+        <v>0.9193765342266964</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.5734513807098505</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.613883107174757</v>
+        <v>2.67077799152505</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.01392929669107</v>
       </c>
       <c r="D1969" t="n">
         <v>-5.38055498634894</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8044559934874544</v>
+        <v>0.8613508778377468</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7162167135325008</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.527304384221277</v>
+        <v>2.58419926857157</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.080264850487891</v>
       </c>
       <c r="D1970" t="n">
         <v>-5.318256987572818</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8957107467947241</v>
+        <v>0.9526056311450164</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7162167135325008</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.593639938018098</v>
+        <v>2.650534822368391</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.788845722877289</v>
       </c>
       <c r="D1971" t="n">
         <v>-5.11646678990766</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6850076982501854</v>
+        <v>0.7419025826004777</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.5181985213633464</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.421031725708989</v>
+        <v>2.477926610059281</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.859135955199464</v>
       </c>
       <c r="D1972" t="n">
         <v>-5.056576108265067</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7792542032293976</v>
+        <v>0.83614908757969</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.458307839720753</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.527256367016721</v>
+        <v>2.584151251367013</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.873763691315508</v>
       </c>
       <c r="D1973" t="n">
         <v>-5.154316652890041</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7547857214954519</v>
+        <v>0.8116806058457442</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.4741971178537331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.532350536252976</v>
+        <v>2.589245420603268</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.872299672140179</v>
       </c>
       <c r="D1974" t="n">
         <v>-5.33065441301297</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6827865982709516</v>
+        <v>0.7396814826212439</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.42508386100389</v>
+        <v>2.481978745354182</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.870791290180108</v>
       </c>
       <c r="D1975" t="n">
         <v>-5.329965040851747</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6815539651753695</v>
+        <v>0.7384488495256618</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.423575479043818</v>
+        <v>2.480470363394111</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.870654157615544</v>
       </c>
       <c r="D1976" t="n">
         <v>-5.33653600590634</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6787884465889684</v>
+        <v>0.7356833309392607</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.419495767446499</v>
+        <v>2.476390651796791</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.870654157615544</v>
       </c>
       <c r="D1977" t="n">
         <v>-5.328582035611568</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6819700347068776</v>
+        <v>0.7388649190571699</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.419495767446499</v>
+        <v>2.476390651796791</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.877035914643349</v>
       </c>
       <c r="D1978" t="n">
         <v>-5.318208659278481</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.692501142267917</v>
+        <v>0.7493960266182094</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.6467324666981682</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.432101550274156</v>
+        <v>2.488996434624448</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.881928288018074</v>
       </c>
       <c r="D1979" t="n">
         <v>-5.190524349484185</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7484672395603602</v>
+        <v>0.8053621239106525</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5190481569038717</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.513604509525459</v>
+        <v>2.570499393875751</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.868682960493946</v>
       </c>
       <c r="D1980" t="n">
         <v>-5.251190939886573</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7109552758752771</v>
+        <v>0.7678501602255694</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.6007464736224054</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.451340191970211</v>
+        <v>2.508235076320503</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.872780663104574</v>
       </c>
       <c r="D1981" t="n">
         <v>-5.186197079952928</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7410505224593638</v>
+        <v>0.7979454068096561</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.57391585901825</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.471536263343332</v>
+        <v>2.528431147693625</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.876941602735652</v>
       </c>
       <c r="D1982" t="n">
         <v>-5.286955715709926</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7049080077876426</v>
+        <v>0.761802892137935</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.6627414277452555</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.422401861738207</v>
+        <v>2.4792967460885</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.88282120526349</v>
       </c>
       <c r="D1983" t="n">
         <v>-5.242752878624025</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7284687451498399</v>
+        <v>0.7853636295001323</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.618538590659355</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.454803166517585</v>
+        <v>2.511698050867877</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.881231205732737</v>
       </c>
       <c r="D1984" t="n">
         <v>-5.279731906287468</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7120871345537103</v>
+        <v>0.7689820189040026</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.475397508061631</v>
+        <v>2.532292392411923</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.932478970915777</v>
       </c>
       <c r="D1985" t="n">
         <v>-5.299789985152309</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7553116681908136</v>
+        <v>0.812206552541106</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.52664527324467</v>
+        <v>2.583540157594963</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.797099142704145</v>
+        <v>3.786633387564929</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.93091967551003</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.258452210052896</v>
+        <v>-5.273048267842481</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7702874828248318</v>
+        <v>0.8213439440592905</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5402269137686115</v>
+        <v>-0.5548229715581969</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.549888642898571</v>
+        <v>2.598025892575112</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240606.xlsx
+++ b/tame_output/ON/bt/strategyON_20240606.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>19.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-24.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-81.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.3%</t>
+          <t>449.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.9%</t>
+          <t>-707.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-294.1%</t>
+          <t>-307.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-154.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-279.5%</t>
+          <t>-299.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.2%</t>
+          <t>-203.9%</t>
         </is>
       </c>
     </row>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.72857792995533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785792</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390431</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607649</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987907</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.72356622940921</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098114</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493425</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722821</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.82635497427919</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011503</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392992</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632787</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883079</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.248764496225443</v>
+        <v>-6.300734316275582</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4775831235292567</v>
+        <v>0.4567951955092013</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.192725750479243</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.261809896045636</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074786</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.155764455019545</v>
+        <v>-6.207734275069684</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4959773987954117</v>
+        <v>0.4751894707753563</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.192725750479243</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.243004154829432</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.915333958214685</v>
+        <v>-5.967303778264823</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5938926741422335</v>
+        <v>0.5731047461221781</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.9522952536743825</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.389005529537226</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.84309139004349</v>
+        <v>-5.895061210093629</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6267190152455315</v>
+        <v>0.6059310872254762</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.9522952536743825</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.392934843372046</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.790093067762102</v>
+        <v>-5.842062887812241</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6485969280754267</v>
+        <v>0.6278090000553713</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.8969589946724437</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.426815182690549</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.681288182282375</v>
+        <v>-5.733258002332514</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6891169534873107</v>
+        <v>0.6683290254672554</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.8969589946724437</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.423813253910542</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.461267384245365</v>
+        <v>-5.513237204295503</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7787043097127291</v>
+        <v>0.7579163816926737</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7557391496044634</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.510124197961945</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.328399695182087</v>
+        <v>-5.380369515232226</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8477455681398638</v>
+        <v>0.826957640119808</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7557391496044634</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.526018380763768</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496266</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.168884591662717</v>
+        <v>-5.220854411712856</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9126974539879136</v>
+        <v>0.8919095259678578</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.5962240460850935</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.622873287315692</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577003</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.02421244656298</v>
+        <v>-5.076182266613118</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9806544145892482</v>
+        <v>0.9598664865691928</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.4515519009853561</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.719764676936974</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942108</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.084087273920672</v>
+        <v>-5.136057093970811</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9427419750475972</v>
+        <v>0.9219540470275418</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.5114267283430483</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.669877271923785</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.76264747767452</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.997287776141663</v>
+        <v>-5.049257596191802</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.999862267481767</v>
+        <v>0.979074339461711</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.5114267283430483</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.692277765246351</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430699</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.999757482603469</v>
+        <v>-5.051727302653608</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9989467862704566</v>
+        <v>0.9781588582504011</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.5138964348048545</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.690868342742679</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003607</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.068127668927479</v>
+        <v>-5.120097488977619</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9826056342155547</v>
+        <v>0.9618177061954989</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5046207357686395</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.70744068463911</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508376</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.176665849843613</v>
+        <v>-5.228635669893753</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9296270704809921</v>
+        <v>0.9088391424609363</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5046207357686395</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.697877393271002</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.207659009172318</v>
+        <v>-5.259628829222458</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.741939371789897</v>
+        <v>0.7211514437698412</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5046207357686395</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.522586958311388</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205904</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.03218474937985</v>
+        <v>-5.084154569429989</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8166963076986722</v>
+        <v>0.7959083796786164</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5046207357686395</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.527154190303176</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.143121002021099</v>
+        <v>-5.195090822071238</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.74806383540338</v>
+        <v>0.7272759073833241</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5046207357686395</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.502896219064383</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.7732102971113</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.346147579564332</v>
+        <v>-5.398117399614471</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6699845896059919</v>
+        <v>0.6491966615859361</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.7076473133118729</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.384211657758349</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264169</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.188221980629039</v>
+        <v>-5.240191800679178</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7433272156122417</v>
+        <v>0.7225392875921859</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.7076473133118729</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.394384044190481</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742305</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.101978517602661</v>
+        <v>-5.153948337652801</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.772770871396653</v>
+        <v>0.7519829433765972</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.7076473133118729</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.389330314764341</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316053</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.147285337001641</v>
+        <v>-5.19925515705178</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7464239190815865</v>
+        <v>0.7256359910615306</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.7484574763211037</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.356619992403329</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803197</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.176318441703942</v>
+        <v>-5.228288261754082</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7353625502337677</v>
+        <v>0.7145746222137119</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.7484574763211037</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.35717186543643</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.083507960253082</v>
+        <v>-5.135477780303222</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7017594347054774</v>
+        <v>0.6809715066854216</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.6556469948702444</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.342130846198311</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560431</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.12789742958251</v>
+        <v>-5.179867249632649</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6858771228983072</v>
+        <v>0.6650891948782514</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.700036464199672</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.317370640525255</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472743</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.01522621134626</v>
+        <v>-5.067196031396399</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7260213187045301</v>
+        <v>0.7052333906844743</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5873652459634219</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.380049079978729</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.902849210163587</v>
+        <v>-4.954819030213726</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7764634150082665</v>
+        <v>0.7556754869882107</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5873652459634219</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.385540375809396</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.68959784049887</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.101083779050318</v>
+        <v>-5.153053599100457</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7086667892221135</v>
+        <v>0.6878788612020577</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.7855998148501525</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.278096836245897</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.184085060075597</v>
+        <v>-5.236054880125736</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5138219968126552</v>
+        <v>0.4930340687925994</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.8041706993773262</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.136491917560329</v>
+        <v>2.105310025530246</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729275</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.292699138518928</v>
+        <v>-5.344668958569067</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.590526026154528</v>
+        <v>0.5697380981344722</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.8041706993773262</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.256641578279534</v>
+        <v>2.225459686249451</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190775</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.379297721500031</v>
+        <v>-5.43126754155017</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5703996190644101</v>
+        <v>0.5496116910443543</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.8041706993773262</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.271154604381857</v>
+        <v>2.239972712351774</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913431</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.34091405894188</v>
+        <v>-5.392883878992019</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5831725254300393</v>
+        <v>0.5623845974099835</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.765787036819175</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.291604243259116</v>
+        <v>2.260422351229034</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.75114719753249</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.163797728906713</v>
+        <v>-5.215767548956853</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6507480862894073</v>
+        <v>0.6299601582693515</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.765787036819175</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.288333272104418</v>
+        <v>2.257151380074335</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793907</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.13409560493042</v>
+        <v>-5.186065424980559</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.663312327641838</v>
+        <v>0.6425243996217822</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7182873419843501</v>
+        <v>-0.7702571620344884</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.286334588737144</v>
+        <v>2.255152696707061</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.75072937701124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.954720183691652</v>
+        <v>-5.006690003741792</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7288494714437594</v>
+        <v>0.7080615434237036</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5615105838136314</v>
+        <v>-0.6134804038637697</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.374187618945989</v>
+        <v>2.343005726915906</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982236</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.999734397212258</v>
+        <v>-5.051704217262397</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.691651241367107</v>
+        <v>0.6708633133470512</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.591859479128236</v>
+        <v>-0.6438292991783743</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.336785737088816</v>
+        <v>2.305603845058733</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.266738907484693</v>
+        <v>-5.318708727534832</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5905409995970787</v>
+        <v>0.5697530715770229</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7862225171711845</v>
+        <v>-0.8381923372213228</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.225859476601993</v>
+        <v>2.19467758457191</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.367936688921866</v>
+        <v>-5.419906508972005</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5492658089187108</v>
+        <v>0.528477880898655</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.9066011507666419</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.184018110371303</v>
+        <v>2.15283621834122</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815463</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.335461102751093</v>
+        <v>-5.387430922801233</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5598560049413366</v>
+        <v>0.5390680769212808</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.9066011507666419</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.18161807192562</v>
+        <v>2.150436179895537</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.316422975043796</v>
+        <v>-5.368392795093936</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5639959752325003</v>
+        <v>0.5432080472124445</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.9647847620978365</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.143232624335147</v>
+        <v>2.112050732305065</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131258</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.347549606194415</v>
+        <v>-5.399519426244554</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7291271917109334</v>
+        <v>0.7083392636908776</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.9647847620978365</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.320814493273828</v>
+        <v>2.289632601243746</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067873</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.399869986795206</v>
+        <v>-5.451839806845346</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7090323684567506</v>
+        <v>0.6882444404366947</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.9298379020889643</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.342615938265285</v>
+        <v>2.311434046235202</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.78742558078913</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.420127285324164</v>
+        <v>-5.472097105374304</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7069379794420931</v>
+        <v>0.6861500514220373</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.9298379020889643</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.348624468662211</v>
+        <v>2.317442576632128</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519915</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.01139285002782</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.272384315089162</v>
+        <v>-5.527936202893068</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9020826996784086</v>
+        <v>0.7429670602065537</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.9752016389826238</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.585356415145455</v>
+        <v>2.369376982287954</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.014186471559301</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.374398997620383</v>
+        <v>-5.629950885424289</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8640704481974009</v>
+        <v>0.7049548087255459</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.9752016389826238</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.588150036676936</v>
+        <v>2.372170603819435</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394736</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.01484881995096</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.23778965352629</v>
+        <v>-5.493341541330197</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9193765342266964</v>
+        <v>0.7602608947548415</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5734513807098505</v>
+        <v>-0.8385922948885313</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.67077799152505</v>
+        <v>2.454798558667549</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890618</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.01392929669107</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.38055498634894</v>
+        <v>-5.636106874152847</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8613508778377468</v>
+        <v>0.7022352383658919</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.9813576277111816</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.58419926857157</v>
+        <v>2.368219835714069</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798433</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.080264850487891</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.318256987572818</v>
+        <v>-5.573808875376725</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9526056311450164</v>
+        <v>0.7934899916731615</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.9813576277111816</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.650534822368391</v>
+        <v>2.43455538951089</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.788845722877289</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.11646678990766</v>
+        <v>-5.372018677711567</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7419025826004777</v>
+        <v>0.5827869431286228</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5181985213633464</v>
+        <v>-0.7833394355420272</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.477926610059281</v>
+        <v>2.261947177201781</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.859135955199464</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.056576108265067</v>
+        <v>-5.312127996068973</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.83614908757969</v>
+        <v>0.6770334481078351</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.458307839720753</v>
+        <v>-0.7234487538994337</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.584151251367013</v>
+        <v>2.368171818509512</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319552</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.873763691315508</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.154316652890041</v>
+        <v>-5.409868540693948</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8116806058457442</v>
+        <v>0.6525649663738893</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4741971178537331</v>
+        <v>-0.739338032032414</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.589245420603268</v>
+        <v>2.373265987745767</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.83181903248939</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.872299672140179</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.33065441301297</v>
+        <v>-5.586206300816877</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7396814826212439</v>
+        <v>0.580565843149389</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.9156757921553434</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.481978745354182</v>
+        <v>2.265999312496682</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.8364116723978</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.870791290180108</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.329965040851747</v>
+        <v>-5.585516928655654</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7384488495256618</v>
+        <v>0.5793332100538069</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.9156757921553434</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.480470363394111</v>
+        <v>2.26449093053661</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024968</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.870654157615544</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.33653600590634</v>
+        <v>-5.592087893710247</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7356833309392607</v>
+        <v>0.5765676914674058</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.9222467572099363</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.476390651796791</v>
+        <v>2.260411218939291</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863231</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.870654157615544</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.328582035611568</v>
+        <v>-5.584133923415474</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7388649190571699</v>
+        <v>0.579749279585315</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.9222467572099363</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.476390651796791</v>
+        <v>2.260411218939291</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.83304018194759</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.877035914643349</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.318208659278481</v>
+        <v>-5.573760547082387</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7493960266182094</v>
+        <v>0.5902803871463544</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6467324666981682</v>
+        <v>-0.911873380876849</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.488996434624448</v>
+        <v>2.273017001766948</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326883</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.881928288018074</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.190524349484185</v>
+        <v>-5.446076237288091</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8053621239106525</v>
+        <v>0.6462464844387976</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5190481569038717</v>
+        <v>-0.7841890710825525</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.570499393875751</v>
+        <v>2.35451996101825</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314558</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.868682960493946</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.251190939886573</v>
+        <v>-5.506742827690481</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7678501602255694</v>
+        <v>0.608734520753714</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6007464736224054</v>
+        <v>-0.8658873878010862</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.508235076320503</v>
+        <v>2.292255643463002</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690033</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.872780663104574</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.186197079952928</v>
+        <v>-5.441748967756835</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7979454068096561</v>
+        <v>0.6388297673378007</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.57391585901825</v>
+        <v>-0.8390567731969308</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.528431147693625</v>
+        <v>2.312451714836124</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674316</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.876941602735652</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.286955715709926</v>
+        <v>-5.542507603513833</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.761802892137935</v>
+        <v>0.6026872526660796</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6627414277452555</v>
+        <v>-0.9278823419239363</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.4792967460885</v>
+        <v>2.263317313230999</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163225</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.88282120526349</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.242752878624025</v>
+        <v>-5.498304766427933</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7853636295001323</v>
+        <v>0.6262479900282769</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.618538590659355</v>
+        <v>-0.8836795048380358</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.511698050867877</v>
+        <v>2.295718618010376</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.83822866302291</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.881231205732737</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.279731906287468</v>
+        <v>-5.535283794091375</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7689820189040026</v>
+        <v>0.6098663794321473</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5815646888680245</v>
+        <v>-0.8467056030467053</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.532292392411923</v>
+        <v>2.316312959554422</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042145</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.932478970915777</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.299789985152309</v>
+        <v>-5.555341872956216</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.812206552541106</v>
+        <v>0.6530909130692506</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.5815646888680245</v>
+        <v>-0.8467056030467053</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.583540157594963</v>
+        <v>2.367560724737462</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.786633387564929</v>
+        <v>3.474272063894698</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.93091967551003</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.273048267842481</v>
+        <v>-5.463327282193291</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8213439440592905</v>
+        <v>0.688337453968674</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5548229715581969</v>
+        <v>-0.7546910122837808</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.598025892575112</v>
+        <v>2.42121018378947</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240606.xlsx
+++ b/tame_output/ON/bt/strategyON_20240606.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.5%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-683.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.4%</t>
+          <t>453.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-707.9%</t>
+          <t>-678.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,37 +1135,37 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-274.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-41.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-307.4%</t>
+          <t>-295.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.1%</t>
+          <t>-294.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.3%</t>
+          <t>-155.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-299.5%</t>
+          <t>-266.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.1%</t>
+          <t>-176.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-203.9%</t>
+          <t>-183.9%</t>
         </is>
       </c>
     </row>
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.075321942939625</v>
+        <v>-4.988958881646289</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.093586332541187</v>
+        <v>1.128131557058521</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8276279496083235</v>
+        <v>-0.7079093600977777</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.62749476426579</v>
+        <v>2.699325917972117</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.310015937072177</v>
+        <v>-5.223652875778841</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9879935098902566</v>
+        <v>1.022538734407591</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.7015730928685225</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.619581299605434</v>
+        <v>2.691412453311761</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.64567858430263</v>
+        <v>-5.559315523009293</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8523090426540407</v>
+        <v>0.8868542671713748</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.7015730928685225</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.618161891261399</v>
+        <v>2.689993044967726</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.009304829202943</v>
+        <v>-5.922941767909607</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7133461049281569</v>
+        <v>0.7478913294454914</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9195133192461942</v>
+        <v>-0.7997947297356484</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.565716469375365</v>
+        <v>2.637547623081693</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.288069150548353</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.6010948913958241</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.215824103545207</v>
+        <v>-1.096105514034661</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.387184513801789</v>
+        <v>2.459015667508116</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.696657927729031</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.4364209245383117</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.504694291215339</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.140792791508141</v>
+        <v>2.212623945214468</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-6.973234028044864</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.3209759168834392</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.504694291215339</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.135978223979602</v>
+        <v>2.207809377685929</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.389625902331861</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.1524132177775179</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.504694291215339</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.133972274588479</v>
+        <v>2.205803428294806</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.792600906165847</v>
+        <v>-7.70623784487251</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.001481906912602859</v>
+        <v>0.03602713142993741</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.504694291215339</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.144230965257158</v>
+        <v>2.216062118963485</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.138475728150656</v>
+        <v>-8.052112666857319</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1407684567356258</v>
+        <v>-0.1062232322182912</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.504694291215339</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.140330530402853</v>
+        <v>2.21216168410918</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.30205560633504</v>
+        <v>-8.215692545041703</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2077954879543786</v>
+        <v>-0.1732502634370436</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.504694291215339</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.138735450457854</v>
+        <v>2.210566604164181</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.598716948145238</v>
+        <v>-8.512353886851901</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3226810487492497</v>
+        <v>-0.2881358242319148</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.573437426949218</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.173099698653063</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.803748128919555</v>
+        <v>-8.717385067626218</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4087198255933795</v>
+        <v>-0.3741746010760445</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.573437426949218</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.16907339411866</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.186749517662186</v>
+        <v>-9.100386456368849</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5620224824120159</v>
+        <v>-0.5274772578946809</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.573437426949218</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.168971292797075</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.36861930864722</v>
+        <v>-9.282256247353883</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6321988828345995</v>
+        <v>-0.5976536583172649</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.755307217934253</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>2.062420934177484</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.728149631151222</v>
+        <v>-9.641786569857885</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7706607085381503</v>
+        <v>-0.7361154840208153</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.755307217934253</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>2.067771237475535</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.778498694605444</v>
+        <v>-9.692135633312107</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7828843139626613</v>
+        <v>-0.7483390894453268</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.805656281388475</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>2.045477819360179</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.87611797202684</v>
+        <v>-9.789754910733503</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8188902743094508</v>
+        <v>-0.7843450497921163</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-1.903275558809872</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.989948003529109</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.02364406003248</v>
+        <v>-9.937280998739146</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8750071531901358</v>
+        <v>-0.8404619286728012</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.050801646815515</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.904325907047296</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.22790223536235</v>
+        <v>-10.14153917406901</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9511972262034387</v>
+        <v>-0.9166520016861046</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.178440591429504</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.833255737397545</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.36971200956913</v>
+        <v>-10.2833489482758</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.003438581401718</v>
+        <v>-0.9688933568843834</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.34971938907508</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.734971013294636</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.29624217790169</v>
+        <v>-10.20987911660835</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9586789472413173</v>
+        <v>-0.9241337227239823</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.276249557407631</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.794424613788526</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.47136659528823</v>
+        <v>-10.38500353399489</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.014173493448418</v>
+        <v>-0.9796282689310836</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.451373974794175</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.703905184104116</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.70581868930272</v>
+        <v>-10.61945562800938</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.11517349595581</v>
+        <v>-1.080628271438475</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.451373974794175</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.69668601920252</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.99362253383996</v>
+        <v>-10.90725947254662</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.236967224544682</v>
+        <v>-1.202422000027347</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.739177819331413</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.517331521706201</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.04640868944028</v>
+        <v>-10.96004562814695</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.256965896946256</v>
+        <v>-1.222420672428921</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.83485330591381</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.461042019595319</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.17244548280857</v>
+        <v>-11.08608242151524</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.304686885664457</v>
+        <v>-1.270141661147122</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.809601683104068</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.478886721910279</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.12042996883976</v>
+        <v>-11.03406690754642</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.279890344390531</v>
+        <v>-1.245345119873196</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.809601683104068</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.48287705759668</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.26210181056388</v>
+        <v>-11.17573874927054</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.338034307978921</v>
+        <v>-1.303489083461586</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.809601683104068</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.481401830697939</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.21251096613905</v>
+        <v>-11.12614790484571</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.303144560044114</v>
+        <v>-1.26859933552678</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.760010838679234</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.526209747517711</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.19970357313427</v>
+        <v>-11.11334051184093</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.311072736488888</v>
+        <v>-1.276527511971553</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.808866613688135</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.483845148865688</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.97385842041486</v>
+        <v>-10.88749535912152</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.211155602364915</v>
+        <v>-1.17661037784758</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.766939938100971</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.518580227254195</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.84927976407727</v>
+        <v>-10.76291670278393</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.160184995273819</v>
+        <v>-1.125639770756484</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.766939938100971</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.519719371810254</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.90217505212155</v>
+        <v>-10.81581199082822</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.178709336329426</v>
+        <v>-1.144164111812091</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.761984592012525</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.525326353625429</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83004187683367</v>
+        <v>-10.74367881554034</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.144122361975637</v>
+        <v>-1.109577137458302</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.761984592012525</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.531060057864065</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.75867548422403</v>
+        <v>-10.67231242293069</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.125313067325643</v>
+        <v>-1.090767842808308</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.690618199402877</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.564142631035989</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.49483861701996</v>
+        <v>-10.40847555572662</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.029661801756923</v>
+        <v>-0.9951165772395885</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.690618199402877</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.554259149723081</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.22759681615156</v>
+        <v>-10.14123375485822</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9245996419089377</v>
+        <v>-0.8900544173916027</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.690618199402877</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.552424589223708</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.12968977747507</v>
+        <v>-10.04332671618173</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8857371414118025</v>
+        <v>-0.8511919168944675</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.62263244954232</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.592915724166581</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.10573623649911</v>
+        <v>-10.01937317520577</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8754872188759255</v>
+        <v>-0.8409419943585905</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.598678908566363</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.607956354897649</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.841676298176314</v>
+        <v>-9.755313236882976</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7831235597085588</v>
+        <v>-0.7485783351912239</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.334618970243567</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.753132001729574</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.134596674671476</v>
+        <v>-9.048233613378139</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5030787439669249</v>
+        <v>-0.4685335194495899</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.334618970243567</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.750344968069274</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.094412376305286</v>
+        <v>-9.008049315011949</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4866614007326073</v>
+        <v>-0.4521161762152723</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.294434671877376</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.774799170976829</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.014342580767481</v>
+        <v>-8.927979519474144</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4552666612967284</v>
+        <v>-0.4207214367793934</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.214364876339572</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.822207869520269</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.780861358537884</v>
+        <v>-8.694498297244547</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3539497435670369</v>
+        <v>-0.3194045190497024</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-1.980883654109973</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.97022103169588</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.631194967530369</v>
+        <v>-8.544831906237032</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2969753974769906</v>
+        <v>-0.2624301729596556</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-1.887980162867437</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>2.023070916128443</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.498919493899482</v>
+        <v>-8.412556432606145</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2486977212776087</v>
+        <v>-0.2141524967602737</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-1.755704689236551</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>2.097803687054002</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.308319819226329</v>
+        <v>-8.221956757932992</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1696427907207103</v>
+        <v>-0.1350975662033758</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.565105014563398</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.21497855254553</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.059320020542748</v>
+        <v>-7.972956959249411</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.05713653002361907</v>
+        <v>-0.02259130550628452</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.565105014563398</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.227884893769189</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.164910010315852</v>
+        <v>-8.078546949022515</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2273484555320797</v>
+        <v>-0.1928032310147447</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.670695004336502</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>2.036554970306108</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.183644912434449</v>
+        <v>-8.097281851141112</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1862980745024321</v>
+        <v>-0.1517528499850975</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.676291013996633</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>2.081741706387115</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.03570487102685</v>
+        <v>-7.949341809733513</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2470009806275599</v>
+        <v>-0.2124557561102254</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.655970098088076</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.974055333244082</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.018546720895555</v>
+        <v>-7.932183659602218</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2488517068285203</v>
+        <v>-0.2143064823111858</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.638811947956782</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.97563623706938</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.974998314124865</v>
+        <v>-7.888635252831528</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2383929562153373</v>
+        <v>-0.2038477316980027</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.638811947956782</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.968675624974287</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.732849920671007</v>
+        <v>-7.64648685937767</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1270712444526509</v>
+        <v>-0.09252601993531639</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.638811947956782</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.98313797935543</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.624590783548485</v>
+        <v>-7.538227722255148</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.08923546914444724</v>
+        <v>-0.05469024462711269</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.638811947956782</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.977670099814625</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.501299648731354</v>
+        <v>-7.414936587438017</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.04242092120701813</v>
+        <v>-0.007875696689683576</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.515520813139651</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>2.04914287471548</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.480150449827911</v>
+        <v>-7.393787388534574</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02626026340831578</v>
+        <v>0.008284961109019218</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.494371614236208</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>2.069533372294872</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.236385007844467</v>
+        <v>-7.15002194655113</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.06702662173211271</v>
+        <v>0.1015718462494477</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.494371614236208</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>2.065314080641922</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.134622187567172</v>
+        <v>-7.048259126273835</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1098560637630466</v>
+        <v>0.1444012882803816</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.481152545843779</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>2.075369835597396</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.884771793618097</v>
+        <v>-6.79840873232476</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2025382963263787</v>
+        <v>0.2370835208437136</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.481152545843779</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>2.068111910581098</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.708879701150664</v>
+        <v>-6.622516639857327</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2764942568340008</v>
+        <v>0.3110394813513353</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.481152545843779</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>2.071711034101746</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.537433238128201</v>
+        <v>-6.451070176834864</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3584003480975397</v>
+        <v>0.3929455726148743</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.309706082821316</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.187906417969778</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.312400238459378</v>
+        <v>-6.226037177166041</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4474340255813658</v>
+        <v>0.4819792500987008</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.084673083152493</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.321946695387369</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.300734316275582</v>
+        <v>-6.162401434932106</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4567951955092013</v>
+        <v>0.5121283480465917</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.192725750479243</v>
+        <v>-1.021037340918558</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.261809896045636</v>
+        <v>2.364822941782047</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074786</v>
+        <v>3.798814771074787</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.207734275069684</v>
+        <v>-6.069401393726208</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4751894707753563</v>
+        <v>0.5305226233127467</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.192725750479243</v>
+        <v>-1.021037340918558</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.243004154829432</v>
+        <v>2.346017200565842</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.967303778264823</v>
+        <v>-5.828970896921348</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5731047461221781</v>
+        <v>0.628437898659568</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9522952536743825</v>
+        <v>-0.7806068441136982</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.389005529537226</v>
+        <v>2.492018575273636</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.895061210093629</v>
+        <v>-5.756728328750153</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6059310872254762</v>
+        <v>0.6612642397628661</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9522952536743825</v>
+        <v>-0.7806068441136982</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.392934843372046</v>
+        <v>2.495947889108456</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.842062887812241</v>
+        <v>-5.703730006468765</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6278090000553713</v>
+        <v>0.6831421525927612</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8969589946724437</v>
+        <v>-0.7252705851117593</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.426815182690549</v>
+        <v>2.529828228426959</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.733258002332514</v>
+        <v>-5.594925120989038</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6683290254672554</v>
+        <v>0.7236621780046457</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8969589946724437</v>
+        <v>-0.7252705851117593</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.423813253910542</v>
+        <v>2.526826299646953</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.513237204295503</v>
+        <v>-5.374904322952028</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7579163816926737</v>
+        <v>0.8132495342300641</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7557391496044634</v>
+        <v>-0.5840507400437791</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.510124197961945</v>
+        <v>2.613137243698355</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.380369515232226</v>
+        <v>-5.24203663388875</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.826957640119808</v>
+        <v>0.8822907926571983</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7557391496044634</v>
+        <v>-0.5840507400437791</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.526018380763768</v>
+        <v>2.629031426500179</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.220854411712856</v>
+        <v>-5.08252153036938</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8919095259678578</v>
+        <v>0.9472426785052481</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5962240460850935</v>
+        <v>-0.4245356365244092</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.622873287315692</v>
+        <v>2.725886333052102</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.076182266613118</v>
+        <v>-4.937849385269643</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9598664865691928</v>
+        <v>1.015199639106583</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4515519009853561</v>
+        <v>-0.2798634914246718</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.719764676936974</v>
+        <v>2.822777722673385</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.136057093970811</v>
+        <v>-4.997724212627335</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9219540470275418</v>
+        <v>0.9772871995649319</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5114267283430483</v>
+        <v>-0.3397383187823639</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.669877271923785</v>
+        <v>2.772890317660195</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.049257596191802</v>
+        <v>-4.910924714848326</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.979074339461711</v>
+        <v>1.034407491999102</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5114267283430483</v>
+        <v>-0.3397383187823639</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.692277765246351</v>
+        <v>2.795290810982761</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.051727302653608</v>
+        <v>-4.913394421310132</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9781588582504011</v>
+        <v>1.033492010787791</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5138964348048545</v>
+        <v>-0.34220802524417</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.690868342742679</v>
+        <v>2.79388138847909</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.120097488977619</v>
+        <v>-4.981764607634142</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9618177061954989</v>
+        <v>1.017150858732889</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5046207357686395</v>
+        <v>-0.3329323262079551</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.70744068463911</v>
+        <v>2.810453730375521</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508376</v>
+        <v>3.714179139508375</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.228635669893753</v>
+        <v>-5.090302788550276</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9088391424609363</v>
+        <v>0.9641722949983271</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5046207357686395</v>
+        <v>-0.3329323262079551</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.697877393271002</v>
+        <v>2.800890439007412</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.710906731417707</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.259628829222458</v>
+        <v>-5.121295947878981</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7211514437698412</v>
+        <v>0.776484596307232</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5046207357686395</v>
+        <v>-0.3329323262079551</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.522586958311388</v>
+        <v>2.625600004047799</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205904</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.084154569429989</v>
+        <v>-4.945821688086513</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7959083796786164</v>
+        <v>0.8512415322160072</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5046207357686395</v>
+        <v>-0.3329323262079551</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.527154190303176</v>
+        <v>2.630167236039587</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.195090822071238</v>
+        <v>-5.056757940727762</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7272759073833241</v>
+        <v>0.7826090599207145</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5046207357686395</v>
+        <v>-0.3329323262079551</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.502896219064383</v>
+        <v>2.605909264800794</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.7732102971113</v>
+        <v>3.773210297111299</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.398117399614471</v>
+        <v>-5.259784518270995</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6491966615859361</v>
+        <v>0.7045298141233269</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7076473133118729</v>
+        <v>-0.5359589037511885</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.384211657758349</v>
+        <v>2.487224703494759</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264169</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.240191800679178</v>
+        <v>-5.101858919335702</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7225392875921859</v>
+        <v>0.7778724401295762</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7076473133118729</v>
+        <v>-0.5359589037511885</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.394384044190481</v>
+        <v>2.497397089926892</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742305</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.153948337652801</v>
+        <v>-5.015615456309324</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7519829433765972</v>
+        <v>0.807316095913988</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7076473133118729</v>
+        <v>-0.5359589037511885</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.389330314764341</v>
+        <v>2.492343360500752</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316053</v>
+        <v>3.752027499316052</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.19925515705178</v>
+        <v>-5.060922275708304</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7256359910615306</v>
+        <v>0.7809691435989214</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7484574763211037</v>
+        <v>-0.5767690667604193</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.356619992403329</v>
+        <v>2.459633038139739</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803197</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.228288261754082</v>
+        <v>-5.089955380410605</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7145746222137119</v>
+        <v>0.7699077747511027</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7484574763211037</v>
+        <v>-0.5767690667604193</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.35717186543643</v>
+        <v>2.460184911172841</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.135477780303222</v>
+        <v>-4.997144898959745</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6809715066854216</v>
+        <v>0.736304659222812</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6556469948702444</v>
+        <v>-0.4839585853095599</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.342130846198311</v>
+        <v>2.445143891934722</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560431</v>
+        <v>3.74828581656043</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.179867249632649</v>
+        <v>-5.041534368289173</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6650891948782514</v>
+        <v>0.7204223474156417</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.700036464199672</v>
+        <v>-0.5283480546389876</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.317370640525255</v>
+        <v>2.420383686261666</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472743</v>
+        <v>3.721077195472742</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.067196031396399</v>
+        <v>-4.928863150052923</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7052333906844743</v>
+        <v>0.7605665432218649</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5873652459634219</v>
+        <v>-0.4156768364027374</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.380049079978729</v>
+        <v>2.483062125715139</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798542</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.954819030213726</v>
+        <v>-4.81648614887025</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7556754869882107</v>
+        <v>0.8110086395256013</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5873652459634219</v>
+        <v>-0.4156768364027374</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.385540375809396</v>
+        <v>2.488553421545806</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049887</v>
+        <v>3.689597840498869</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.153053599100457</v>
+        <v>-5.014720717756981</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6878788612020577</v>
+        <v>0.743212013739448</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7855998148501525</v>
+        <v>-0.613911405289468</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.278096836245897</v>
+        <v>2.381109881982307</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.236054880125736</v>
+        <v>-5.09772199878226</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4930340687925994</v>
+        <v>0.5483672213299897</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.8041706993773262</v>
+        <v>-0.6324822898166418</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.105310025530246</v>
+        <v>2.208323071266656</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729275</v>
+        <v>3.682716310729274</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.344668958569067</v>
+        <v>-5.206336077225591</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5697380981344722</v>
+        <v>0.625071250671863</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.8041706993773262</v>
+        <v>-0.6324822898166418</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.225459686249451</v>
+        <v>2.328472731985862</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190775</v>
+        <v>3.733012441190773</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.43126754155017</v>
+        <v>-5.292934660206694</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5496116910443543</v>
+        <v>0.6049448435817446</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.8041706993773262</v>
+        <v>-0.6324822898166418</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.239972712351774</v>
+        <v>2.342985758088185</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913431</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.392883878992019</v>
+        <v>-5.254550997648542</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5623845974099835</v>
+        <v>0.6177177499473738</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.765787036819175</v>
+        <v>-0.5940986272584906</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.260422351229034</v>
+        <v>2.363435396965444</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753249</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.215767548956853</v>
+        <v>-5.077434667613376</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6299601582693515</v>
+        <v>0.6852933108067423</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.765787036819175</v>
+        <v>-0.5940986272584906</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.257151380074335</v>
+        <v>2.360164425810746</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793907</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.186065424980559</v>
+        <v>-5.047732543637083</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6425243996217822</v>
+        <v>0.697857552159173</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7702571620344884</v>
+        <v>-0.5985687524738039</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.255152696707061</v>
+        <v>2.358165742443471</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072937701124</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.006690003741792</v>
+        <v>-4.868357122398315</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7080615434237036</v>
+        <v>0.7633946959610942</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6134804038637697</v>
+        <v>-0.4417919943030852</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.343005726915906</v>
+        <v>2.446018772652317</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982236</v>
+        <v>3.716991718982234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.051704217262397</v>
+        <v>-4.913371335918921</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6708633133470512</v>
+        <v>0.7261964658844418</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6438292991783743</v>
+        <v>-0.4721408896176899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.305603845058733</v>
+        <v>2.408616890795144</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.318708727534832</v>
+        <v>-5.180375846191356</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5697530715770229</v>
+        <v>0.6250862241144133</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8381923372213228</v>
+        <v>-0.6665039276606384</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.19467758457191</v>
+        <v>2.29769063030832</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760817</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.419906508972005</v>
+        <v>-5.281573627628529</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.528477880898655</v>
+        <v>0.5838110334360458</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9066011507666419</v>
+        <v>-0.7349127412059575</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.15283621834122</v>
+        <v>2.25584926407763</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815463</v>
+        <v>3.705571661815461</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.387430922801233</v>
+        <v>-5.249098041457756</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5390680769212808</v>
+        <v>0.5944012294586716</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9066011507666419</v>
+        <v>-0.7349127412059575</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.150436179895537</v>
+        <v>2.253449225631947</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.368392795093936</v>
+        <v>-5.230059913750459</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5432080472124445</v>
+        <v>0.5985411997498353</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9647847620978365</v>
+        <v>-0.793096352537152</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.112050732305065</v>
+        <v>2.215063778041475</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131258</v>
+        <v>3.731064473131256</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.399519426244554</v>
+        <v>-5.261186544901078</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7083392636908776</v>
+        <v>0.7636724162282684</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9647847620978365</v>
+        <v>-0.793096352537152</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.289632601243746</v>
+        <v>2.392645646980156</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067873</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.451839806845346</v>
+        <v>-5.313506925501869</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6882444404366947</v>
+        <v>0.7435775929740851</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9298379020889643</v>
+        <v>-0.7581494925282799</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.311434046235202</v>
+        <v>2.414447091971613</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078913</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.472097105374304</v>
+        <v>-5.333764224030827</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6861500514220373</v>
+        <v>0.7414832039594281</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9298379020889643</v>
+        <v>-0.7581494925282799</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.317442576632128</v>
+        <v>2.420455622368539</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.527936202893068</v>
+        <v>-5.186021253795825</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7429670602065537</v>
+        <v>0.8797330398454508</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.9752016389826238</v>
+        <v>-0.5903421352933967</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.369376982287954</v>
+        <v>2.60029268450149</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181177</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.629950885424289</v>
+        <v>-5.288035936327046</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7049548087255459</v>
+        <v>0.8417207883644435</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.9752016389826238</v>
+        <v>-0.5903421352933967</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.372170603819435</v>
+        <v>2.603086306032971</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394736</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.493341541330197</v>
+        <v>-5.151426592232953</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7602608947548415</v>
+        <v>0.8970268743937391</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.8385922948885313</v>
+        <v>-0.4537327911993043</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.454798558667549</v>
+        <v>2.685714260881085</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890618</v>
+        <v>3.798239794890616</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.636106874152847</v>
+        <v>-5.294191925055603</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7022352383658919</v>
+        <v>0.839001218004789</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.9813576277111816</v>
+        <v>-0.5964981240219547</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.368219835714069</v>
+        <v>2.599135537927605</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798433</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.573808875376725</v>
+        <v>-5.231893926279481</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7934899916731615</v>
+        <v>0.9302559713120591</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.9813576277111816</v>
+        <v>-0.5964981240219547</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.43455538951089</v>
+        <v>2.665471091724426</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992196</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.372018677711567</v>
+        <v>-5.030103728614323</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5827869431286228</v>
+        <v>0.7195529227675199</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.7833394355420272</v>
+        <v>-0.3984799318528003</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.261947177201781</v>
+        <v>2.492862879415317</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.312127996068973</v>
+        <v>-4.97021304697173</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6770334481078351</v>
+        <v>0.8137994277467326</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.7234487538994337</v>
+        <v>-0.3385892502102068</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.368171818509512</v>
+        <v>2.599087520723048</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319552</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.409868540693948</v>
+        <v>-5.067953591596704</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6525649663738893</v>
+        <v>0.7893309460127864</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.739338032032414</v>
+        <v>-0.354478528343187</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.373265987745767</v>
+        <v>2.604181689959304</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248939</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.586206300816877</v>
+        <v>-5.244291351719633</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.580565843149389</v>
+        <v>0.7173318227882866</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.9156757921553434</v>
+        <v>-0.5308162884661164</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.265999312496682</v>
+        <v>2.496915014710217</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.8364116723978</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.585516928655654</v>
+        <v>-5.24360197955841</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5793332100538069</v>
+        <v>0.7160991896927045</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.9156757921553434</v>
+        <v>-0.5308162884661164</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.26449093053661</v>
+        <v>2.495406632750146</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024968</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.592087893710247</v>
+        <v>-5.250172944613003</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5765676914674058</v>
+        <v>0.7133336711063034</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.9222467572099363</v>
+        <v>-0.5373872535207094</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.260411218939291</v>
+        <v>2.491326921152826</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863231</v>
+        <v>3.821591150863229</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.584133923415474</v>
+        <v>-5.242218974318231</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.579749279585315</v>
+        <v>0.7165152592242121</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.9222467572099363</v>
+        <v>-0.5373872535207094</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.260411218939291</v>
+        <v>2.491326921152826</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83304018194759</v>
+        <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.573760547082387</v>
+        <v>-5.231845597985144</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.5902803871463544</v>
+        <v>0.7270463667852516</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.911873380876849</v>
+        <v>-0.527013877187622</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.273017001766948</v>
+        <v>2.503932703980484</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326883</v>
+        <v>3.822707244326881</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.446076237288091</v>
+        <v>-5.104161288190848</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6462464844387976</v>
+        <v>0.7830124640776952</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.7841890710825525</v>
+        <v>-0.3993295673933256</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.35451996101825</v>
+        <v>2.585435663231786</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314558</v>
+        <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.506742827690481</v>
+        <v>-5.164827878593236</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.608734520753714</v>
+        <v>0.7455005003926116</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.8658873878010862</v>
+        <v>-0.4810278841118593</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.292255643463002</v>
+        <v>2.523171345676538</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690033</v>
+        <v>3.816866067690031</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.441748967756835</v>
+        <v>-5.099834018659591</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6388297673378007</v>
+        <v>0.7755957469766988</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.8390567731969308</v>
+        <v>-0.4541972695077039</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.312451714836124</v>
+        <v>2.54336741704966</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674316</v>
+        <v>3.817961388674314</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.542507603513833</v>
+        <v>-5.200592654416589</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6026872526660796</v>
+        <v>0.7394532323049772</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.9278823419239363</v>
+        <v>-0.5430228382347093</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.263317313230999</v>
+        <v>2.494233015444535</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163225</v>
+        <v>3.826713779163224</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.498304766427933</v>
+        <v>-5.156389817330688</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6262479900282769</v>
+        <v>0.7630139696671745</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.8836795048380358</v>
+        <v>-0.4988200011488089</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.295718618010376</v>
+        <v>2.526634320223912</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83822866302291</v>
+        <v>3.838228663022909</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.535283794091375</v>
+        <v>-5.193368844994131</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6098663794321473</v>
+        <v>0.7466323590710453</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.8467056030467053</v>
+        <v>-0.4618460993574783</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.316312959554422</v>
+        <v>2.547228661767958</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042145</v>
+        <v>3.863924114042143</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.555341872956216</v>
+        <v>-5.213426923858972</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6530909130692506</v>
+        <v>0.7898568927081486</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.8467056030467053</v>
+        <v>-0.4618460993574783</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.367560724737462</v>
+        <v>2.598476426950998</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.474272063894698</v>
+        <v>3.825841490223261</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.463327282193291</v>
+        <v>-5.173496250681081</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.688337453968674</v>
+        <v>0.8042698665735579</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.7546910122837808</v>
+        <v>-0.421915426179588</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.42121018378947</v>
+        <v>2.620875535451985</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240606.xlsx
+++ b/tame_output/ON/bt/strategyON_20240606.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-33.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-81.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-683.9%</t>
+          <t>-692.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.9%</t>
+          <t>452.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-678.9%</t>
+          <t>-693.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-274.0%</t>
+          <t>-277.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.7%</t>
+          <t>-42.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-295.8%</t>
+          <t>-301.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-294.2%</t>
+          <t>-306.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.3%</t>
+          <t>-156.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-266.2%</t>
+          <t>-284.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-176.9%</t>
+          <t>-184.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-183.9%</t>
+          <t>-169.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1986"/>
+  <dimension ref="A1:G1987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.988958881646289</v>
+        <v>-5.075321942939625</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.128131557058521</v>
+        <v>1.093586332541187</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7079093600977777</v>
+        <v>-0.8276279496083235</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.699325917972117</v>
+        <v>2.62749476426579</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.223652875778841</v>
+        <v>-5.310015937072177</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.022538734407591</v>
+        <v>0.9879935098902566</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7015730928685225</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.691412453311761</v>
+        <v>2.619581299605434</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.559315523009293</v>
+        <v>-5.64567858430263</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8868542671713748</v>
+        <v>0.8523090426540407</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7015730928685225</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.689993044967726</v>
+        <v>2.618161891261399</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.922941767909607</v>
+        <v>-6.009304829202943</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7478913294454914</v>
+        <v>0.7133461049281569</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7997947297356484</v>
+        <v>-0.9195133192461942</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.637547623081693</v>
+        <v>2.565716469375365</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.288069150548353</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6010948913958241</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.096105514034661</v>
+        <v>-1.215824103545207</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.459015667508116</v>
+        <v>2.387184513801789</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.696657927729031</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4364209245383117</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.504694291215339</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.212623945214468</v>
+        <v>2.140792791508141</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.973234028044864</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3209759168834392</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.504694291215339</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.207809377685929</v>
+        <v>2.135978223979602</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.389625902331861</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1524132177775179</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.504694291215339</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.205803428294806</v>
+        <v>2.133972274588479</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.70623784487251</v>
+        <v>-7.792600906165847</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03602713142993741</v>
+        <v>0.001481906912602859</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.504694291215339</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.216062118963485</v>
+        <v>2.144230965257158</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.052112666857319</v>
+        <v>-8.138475728150656</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1062232322182912</v>
+        <v>-0.1407684567356258</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.504694291215339</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.21216168410918</v>
+        <v>2.140330530402853</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.215692545041703</v>
+        <v>-8.30205560633504</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1732502634370436</v>
+        <v>-0.2077954879543786</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.504694291215339</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.210566604164181</v>
+        <v>2.138735450457854</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.512353886851901</v>
+        <v>-8.598716948145238</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2881358242319148</v>
+        <v>-0.3226810487492497</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.573437426949218</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.173099698653063</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.717385067626218</v>
+        <v>-8.803748128919555</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3741746010760445</v>
+        <v>-0.4087198255933795</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.573437426949218</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.16907339411866</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.100386456368849</v>
+        <v>-9.186749517662186</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5274772578946809</v>
+        <v>-0.5620224824120159</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.573437426949218</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.168971292797075</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.282256247353883</v>
+        <v>-9.36861930864722</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5976536583172649</v>
+        <v>-0.6321988828345995</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.755307217934253</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.062420934177484</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.641786569857885</v>
+        <v>-9.728149631151222</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7361154840208153</v>
+        <v>-0.7706607085381503</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.755307217934253</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.067771237475535</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.692135633312107</v>
+        <v>-9.778498694605444</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7483390894453268</v>
+        <v>-0.7828843139626613</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.805656281388475</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.045477819360179</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.789754910733503</v>
+        <v>-9.87611797202684</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7843450497921163</v>
+        <v>-0.8188902743094508</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.903275558809872</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.989948003529109</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.937280998739146</v>
+        <v>-10.02364406003248</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8404619286728012</v>
+        <v>-0.8750071531901358</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.050801646815515</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.904325907047296</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.14153917406901</v>
+        <v>-10.22790223536235</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9166520016861046</v>
+        <v>-0.9511972262034387</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.178440591429504</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.833255737397545</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.2833489482758</v>
+        <v>-10.36971200956913</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9688933568843834</v>
+        <v>-1.003438581401718</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.34971938907508</v>
+        <v>-2.469437978585626</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.734971013294636</v>
+        <v>1.663139859588308</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.20987911660835</v>
+        <v>-10.29624217790169</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9241337227239823</v>
+        <v>-0.9586789472413173</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.276249557407631</v>
+        <v>-2.395968146918177</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.794424613788526</v>
+        <v>1.722593460082198</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.38500353399489</v>
+        <v>-10.47136659528823</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9796282689310836</v>
+        <v>-1.014173493448418</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.451373974794175</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.703905184104116</v>
+        <v>1.632074030397789</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.61945562800938</v>
+        <v>-10.70581868930272</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.080628271438475</v>
+        <v>-1.11517349595581</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.451373974794175</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.69668601920252</v>
+        <v>1.624854865496193</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.90725947254662</v>
+        <v>-10.99362253383996</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.202422000027347</v>
+        <v>-1.236967224544682</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.739177819331413</v>
+        <v>-2.858896408841959</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.517331521706201</v>
+        <v>1.445500367999874</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.96004562814695</v>
+        <v>-11.04640868944028</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.222420672428921</v>
+        <v>-1.256965896946256</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.83485330591381</v>
+        <v>-2.954571895424356</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.461042019595319</v>
+        <v>1.389210865888992</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.08608242151524</v>
+        <v>-11.17244548280857</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.270141661147122</v>
+        <v>-1.304686885664457</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.809601683104068</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.478886721910279</v>
+        <v>1.407055568203952</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.03406690754642</v>
+        <v>-11.12042996883976</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.245345119873196</v>
+        <v>-1.279890344390531</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.809601683104068</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.48287705759668</v>
+        <v>1.411045903890353</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.17573874927054</v>
+        <v>-11.26210181056388</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.303489083461586</v>
+        <v>-1.338034307978921</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.809601683104068</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.481401830697939</v>
+        <v>1.409570676991611</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.12614790484571</v>
+        <v>-11.21251096613905</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.26859933552678</v>
+        <v>-1.303144560044114</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.760010838679234</v>
+        <v>-2.87972942818978</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.526209747517711</v>
+        <v>1.454378593811384</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.11334051184093</v>
+        <v>-11.19970357313427</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.276527511971553</v>
+        <v>-1.311072736488888</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.808866613688135</v>
+        <v>-2.928585203198681</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.483845148865688</v>
+        <v>1.41201399515936</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.88749535912152</v>
+        <v>-10.97385842041486</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.17661037784758</v>
+        <v>-1.211155602364915</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.766939938100971</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.518580227254195</v>
+        <v>1.446749073547867</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.76291670278393</v>
+        <v>-10.84927976407727</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.125639770756484</v>
+        <v>-1.160184995273819</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.766939938100971</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.519719371810254</v>
+        <v>1.447888218103926</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.81581199082822</v>
+        <v>-10.90217505212155</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.144164111812091</v>
+        <v>-1.178709336329426</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.761984592012525</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.525326353625429</v>
+        <v>1.453495199919101</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.74367881554034</v>
+        <v>-10.83004187683367</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.109577137458302</v>
+        <v>-1.144122361975637</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.761984592012525</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.531060057864065</v>
+        <v>1.459228904157738</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857792995533</v>
+        <v>3.728577929955331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.67231242293069</v>
+        <v>-10.81868753622064</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.090767842808308</v>
+        <v>-1.149317888124288</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.690618199402877</v>
+        <v>-2.870348840910036</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.564142631035989</v>
+        <v>1.456304246131694</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.40847555572662</v>
+        <v>-10.55485066901657</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9951165772395885</v>
+        <v>-1.053666622555567</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.690618199402877</v>
+        <v>-2.870348840910036</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.554259149723081</v>
+        <v>1.446420764818786</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.14123375485822</v>
+        <v>-10.28760886814817</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8900544173916027</v>
+        <v>-0.9486044627075825</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.690618199402877</v>
+        <v>-2.870348840910036</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.552424589223708</v>
+        <v>1.444586204319412</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.04332671618173</v>
+        <v>-10.18970182947168</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8511919168944675</v>
+        <v>-0.9097419622104472</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.62263244954232</v>
+        <v>-2.802363091049479</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.592915724166581</v>
+        <v>1.485077339262285</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.01937317520577</v>
+        <v>-10.16574828849572</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8409419943585905</v>
+        <v>-0.8994920396745703</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.598678908566363</v>
+        <v>-2.778409550073522</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.607956354897649</v>
+        <v>1.500117969993353</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.755313236882976</v>
+        <v>-9.901688350172925</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7485783351912239</v>
+        <v>-0.8071283805072036</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.334618970243567</v>
+        <v>-2.514349611750725</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.753132001729574</v>
+        <v>1.645293616825279</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839727</v>
+        <v>3.833252747839729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.048233613378139</v>
+        <v>-9.194608726668088</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4685335194495899</v>
+        <v>-0.5270835647655696</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.334618970243567</v>
+        <v>-2.514349611750725</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.750344968069274</v>
+        <v>1.642506583164978</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.008049315011949</v>
+        <v>-9.154424428301898</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4521161762152723</v>
+        <v>-0.5106662215312521</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.294434671877376</v>
+        <v>-2.474165313384534</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.774799170976829</v>
+        <v>1.666960786072534</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.927979519474144</v>
+        <v>-9.074354632764093</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4207214367793934</v>
+        <v>-0.4792714820953732</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.214364876339572</v>
+        <v>-2.39409551784673</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.822207869520269</v>
+        <v>1.714369484615973</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291816</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.694498297244547</v>
+        <v>-8.840873410534495</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3194045190497024</v>
+        <v>-0.3779545643656816</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.980883654109973</v>
+        <v>-2.160614295617132</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.97022103169588</v>
+        <v>1.862382646791585</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785792</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.544831906237032</v>
+        <v>-8.691207019526981</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2624301729596556</v>
+        <v>-0.3209802182756354</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.887980162867437</v>
+        <v>-2.067710804374596</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.023070916128443</v>
+        <v>1.915232531224148</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390431</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.412556432606145</v>
+        <v>-8.558931545896094</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2141524967602737</v>
+        <v>-0.2727025420762534</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.755704689236551</v>
+        <v>-1.935435330743709</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.097803687054002</v>
+        <v>1.989965302149707</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105958</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.221956757932992</v>
+        <v>-8.36833187122294</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1350975662033758</v>
+        <v>-0.1936476115193551</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.565105014563398</v>
+        <v>-1.744835656070556</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.21497855254553</v>
+        <v>2.107140167641235</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.972956959249411</v>
+        <v>-8.119332072539359</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.02259130550628452</v>
+        <v>-0.08114135082226381</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.565105014563398</v>
+        <v>-1.744835656070556</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.227884893769189</v>
+        <v>2.120046508864894</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607649</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.078546949022515</v>
+        <v>-8.224922062312464</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1928032310147447</v>
+        <v>-0.2513532763307245</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.670695004336502</v>
+        <v>-1.850425645843661</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.036554970306108</v>
+        <v>1.928716585401812</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987907</v>
+        <v>3.770422583987909</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.097281851141112</v>
+        <v>-8.243656964431061</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1517528499850975</v>
+        <v>-0.2103028953010768</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.676291013996633</v>
+        <v>-1.856021655503792</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.081741706387115</v>
+        <v>1.97390332148282</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.949341809733513</v>
+        <v>-8.095716923023462</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2124557561102254</v>
+        <v>-0.2710058014262047</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.655970098088076</v>
+        <v>-1.835700739595234</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.974055333244082</v>
+        <v>1.866216948339787</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.72356622940921</v>
+        <v>3.723566229409212</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.932183659602218</v>
+        <v>-8.078558772892167</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2143064823111858</v>
+        <v>-0.2728565276271651</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.638811947956782</v>
+        <v>-1.81854258946394</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.97563623706938</v>
+        <v>1.867797852165085</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098114</v>
+        <v>3.729969716098116</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.888635252831528</v>
+        <v>-8.035010366121476</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2038477316980027</v>
+        <v>-0.262397777013982</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.638811947956782</v>
+        <v>-1.81854258946394</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.968675624974287</v>
+        <v>1.860837240069992</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493425</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.64648685937767</v>
+        <v>-7.792861972667618</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.09252601993531639</v>
+        <v>-0.1510760652512957</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.638811947956782</v>
+        <v>-1.81854258946394</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.98313797935543</v>
+        <v>1.875299594451135</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722821</v>
+        <v>3.828551486722823</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.538227722255148</v>
+        <v>-7.684602835545096</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.05469024462711269</v>
+        <v>-0.113240289943092</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.638811947956782</v>
+        <v>-1.81854258946394</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.977670099814625</v>
+        <v>1.86983171491033</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792051</v>
+        <v>3.828052928792053</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.414936587438017</v>
+        <v>-7.561311700727965</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.007875696689683576</v>
+        <v>-0.06642574200566242</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.515520813139651</v>
+        <v>-1.695251454646809</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.04914287471548</v>
+        <v>1.941304489811186</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.812453678919914</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.393787388534574</v>
+        <v>-7.540162501824522</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.008284961109019218</v>
+        <v>-0.05026508420696008</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.494371614236208</v>
+        <v>-1.674102255743366</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.069533372294872</v>
+        <v>1.961694987390577</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318099</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.15002194655113</v>
+        <v>-7.296397059841078</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1015718462494477</v>
+        <v>0.04302180093346841</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.494371614236208</v>
+        <v>-1.674102255743366</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.065314080641922</v>
+        <v>1.957475695737628</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057532</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.048259126273835</v>
+        <v>-7.194634239563783</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1444012882803816</v>
+        <v>0.08585124296440227</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.481152545843779</v>
+        <v>-1.660883187350937</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.075369835597396</v>
+        <v>1.967531450693101</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427919</v>
+        <v>3.826354974279192</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.79840873232476</v>
+        <v>-6.944783845614708</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2370835208437136</v>
+        <v>0.1785334755277344</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.481152545843779</v>
+        <v>-1.660883187350937</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.068111910581098</v>
+        <v>1.960273525676803</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011503</v>
+        <v>3.835957987011505</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.622516639857327</v>
+        <v>-6.768891753147276</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3110394813513353</v>
+        <v>0.252489436035356</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.481152545843779</v>
+        <v>-1.660883187350937</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.071711034101746</v>
+        <v>1.963872649197452</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392992</v>
+        <v>3.780933911392994</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.451070176834864</v>
+        <v>-6.597445290124813</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3929455726148743</v>
+        <v>0.334395527298895</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.309706082821316</v>
+        <v>-1.489436724328474</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.187906417969778</v>
+        <v>2.080068033065483</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632787</v>
+        <v>3.773765222632789</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.226037177166041</v>
+        <v>-6.37241229045599</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4819792500987008</v>
+        <v>0.4234292047827211</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.084673083152493</v>
+        <v>-1.264403724659651</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.321946695387369</v>
+        <v>2.214108310483074</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883079</v>
+        <v>3.76461787988308</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.162401434932106</v>
+        <v>-6.308776548222055</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5121283480465917</v>
+        <v>0.4535783027306119</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.021037340918558</v>
+        <v>-1.200767982425717</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.364822941782047</v>
+        <v>2.256984556877752</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074787</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.069401393726208</v>
+        <v>-6.215776507016157</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5305226233127467</v>
+        <v>0.471972577996767</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.021037340918558</v>
+        <v>-1.200767982425717</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.346017200565842</v>
+        <v>2.238178815661548</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242297</v>
+        <v>3.797694884242299</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.828970896921348</v>
+        <v>-5.975346010211297</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.628437898659568</v>
+        <v>0.5698878533435887</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7806068441136982</v>
+        <v>-0.9603374856208564</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.492018575273636</v>
+        <v>2.384180190369341</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367688</v>
+        <v>3.821593509367689</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.756728328750153</v>
+        <v>-5.903103442040102</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6612642397628661</v>
+        <v>0.6027141944468868</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7806068441136982</v>
+        <v>-0.9603374856208564</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.495947889108456</v>
+        <v>2.388109504204161</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879969</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.703730006468765</v>
+        <v>-5.850105119758714</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6831421525927612</v>
+        <v>0.6245921072767819</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7252705851117593</v>
+        <v>-0.9050012266189176</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.529828228426959</v>
+        <v>2.421989843522665</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502343</v>
+        <v>3.848616626502345</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.594925120989038</v>
+        <v>-5.741300234278987</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7236621780046457</v>
+        <v>0.665112132688666</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7252705851117593</v>
+        <v>-0.9050012266189176</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.526826299646953</v>
+        <v>2.418987914742658</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.818668951675944</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.374904322952028</v>
+        <v>-5.521279436241977</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8132495342300641</v>
+        <v>0.7546994889140843</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5840507400437791</v>
+        <v>-0.7637813815509373</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.613137243698355</v>
+        <v>2.505298858794061</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.24203663388875</v>
+        <v>-5.388411747178699</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8822907926571983</v>
+        <v>0.823740747341219</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5840507400437791</v>
+        <v>-0.7637813815509373</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.629031426500179</v>
+        <v>2.521193041595883</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496266</v>
+        <v>3.845047386496268</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.08252153036938</v>
+        <v>-5.228896643659329</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9472426785052481</v>
+        <v>0.8886926331892688</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4245356365244092</v>
+        <v>-0.6042662780315674</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.725886333052102</v>
+        <v>2.618047948147808</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577003</v>
+        <v>3.791273551577005</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.937849385269643</v>
+        <v>-5.084224498559592</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.015199639106583</v>
+        <v>0.9566495937906034</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2798634914246718</v>
+        <v>-0.45959413293183</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.822777722673385</v>
+        <v>2.71493933776909</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942108</v>
+        <v>3.73583922294211</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.997724212627335</v>
+        <v>-5.144099325917284</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9772871995649319</v>
+        <v>0.9187371542489524</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3397383187823639</v>
+        <v>-0.5194689602895222</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.772890317660195</v>
+        <v>2.6650519327559</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767452</v>
+        <v>3.762647477674522</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.910924714848326</v>
+        <v>-5.057299828138275</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.034407491999102</v>
+        <v>0.975857446683122</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3397383187823639</v>
+        <v>-0.5194689602895222</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.795290810982761</v>
+        <v>2.687452426078466</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430699</v>
+        <v>3.729146398430701</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.913394421310132</v>
+        <v>-5.059769534600081</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.033492010787791</v>
+        <v>0.9749419654718121</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.34220802524417</v>
+        <v>-0.5219386667513284</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.79388138847909</v>
+        <v>2.686043003574795</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003607</v>
+        <v>3.743220196003609</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.981764607634142</v>
+        <v>-5.128139720924091</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.017150858732889</v>
+        <v>0.9586008134169099</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3329323262079551</v>
+        <v>-0.5126629677151134</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.810453730375521</v>
+        <v>2.702615345471226</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508375</v>
+        <v>3.714179139508378</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.090302788550276</v>
+        <v>-5.236677901840225</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9641722949983271</v>
+        <v>0.9056222496823474</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3329323262079551</v>
+        <v>-0.5126629677151134</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.800890439007412</v>
+        <v>2.693052054103117</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417707</v>
+        <v>3.71090673141771</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.121295947878981</v>
+        <v>-5.26767106116893</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.776484596307232</v>
+        <v>0.7179345509912523</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3329323262079551</v>
+        <v>-0.5126629677151134</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.625600004047799</v>
+        <v>2.517761619143504</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205906</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.945821688086513</v>
+        <v>-5.092196801376462</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8512415322160072</v>
+        <v>0.7926914869000274</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3329323262079551</v>
+        <v>-0.5126629677151134</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.630167236039587</v>
+        <v>2.522328851135291</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225451</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.056757940727762</v>
+        <v>-5.203133054017711</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7826090599207145</v>
+        <v>0.7240590146047352</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3329323262079551</v>
+        <v>-0.5126629677151134</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.605909264800794</v>
+        <v>2.498070879896499</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111299</v>
+        <v>3.773210297111302</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.259784518270995</v>
+        <v>-5.406159631560944</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7045298141233269</v>
+        <v>0.6459797688073472</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5359589037511885</v>
+        <v>-0.7156895452583468</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.487224703494759</v>
+        <v>2.379386318590464</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.101858919335702</v>
+        <v>-5.248234032625651</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7778724401295762</v>
+        <v>0.7193223948135969</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5359589037511885</v>
+        <v>-0.7156895452583468</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.497397089926892</v>
+        <v>2.389558705022597</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742307</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.015615456309324</v>
+        <v>-5.161990569599273</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.807316095913988</v>
+        <v>0.7487660505980083</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5359589037511885</v>
+        <v>-0.7156895452583468</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.492343360500752</v>
+        <v>2.384504975596457</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316052</v>
+        <v>3.752027499316054</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.060922275708304</v>
+        <v>-5.207297388998253</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7809691435989214</v>
+        <v>0.7224190982829417</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5767690667604193</v>
+        <v>-0.7564997082675776</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.459633038139739</v>
+        <v>2.351794653235444</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.753571165803199</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.089955380410605</v>
+        <v>-5.236330493700554</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7699077747511027</v>
+        <v>0.711357729435123</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5767690667604193</v>
+        <v>-0.7564997082675776</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.460184911172841</v>
+        <v>2.352346526268545</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809505</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.997144898959745</v>
+        <v>-5.143520012249694</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.736304659222812</v>
+        <v>0.6777546139068327</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4839585853095599</v>
+        <v>-0.6636892268167183</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.445143891934722</v>
+        <v>2.337305507030427</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.74828581656043</v>
+        <v>3.748285816560433</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.041534368289173</v>
+        <v>-5.187909481579122</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7204223474156417</v>
+        <v>0.6618723020996624</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5283480546389876</v>
+        <v>-0.7080786961461459</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.420383686261666</v>
+        <v>2.312545301357371</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472742</v>
+        <v>3.721077195472745</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.928863150052923</v>
+        <v>-5.075238263342872</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7605665432218649</v>
+        <v>0.7020164979058854</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4156768364027374</v>
+        <v>-0.5954074779098957</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.483062125715139</v>
+        <v>2.375223740810844</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798542</v>
+        <v>3.743047603798544</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.81648614887025</v>
+        <v>-4.962861262160199</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8110086395256013</v>
+        <v>0.7524585942096218</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4156768364027374</v>
+        <v>-0.5954074779098957</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.488553421545806</v>
+        <v>2.380715036641512</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498869</v>
+        <v>3.689597840498872</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.014720717756981</v>
+        <v>-5.161095831046929</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.743212013739448</v>
+        <v>0.6846619684234687</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.613911405289468</v>
+        <v>-0.7936420467966263</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.381109881982307</v>
+        <v>2.273271497078012</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170533</v>
+        <v>3.643069621705332</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.09772199878226</v>
+        <v>-5.244097112072208</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5483672213299897</v>
+        <v>0.4898171760140104</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6324822898166418</v>
+        <v>-0.8122129313238</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.208323071266656</v>
+        <v>2.100484686362361</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729274</v>
+        <v>3.682716310729277</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.206336077225591</v>
+        <v>-5.35271119051554</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.625071250671863</v>
+        <v>0.5665212053558832</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6324822898166418</v>
+        <v>-0.8122129313238</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.328472731985862</v>
+        <v>2.220634347081567</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190773</v>
+        <v>3.733012441190777</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.292934660206694</v>
+        <v>-5.439309773496642</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6049448435817446</v>
+        <v>0.5463947982657653</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6324822898166418</v>
+        <v>-0.8122129313238</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.342985758088185</v>
+        <v>2.23514737318389</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913432</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.254550997648542</v>
+        <v>-5.400926110938491</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6177177499473738</v>
+        <v>0.5591677046313945</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5940986272584906</v>
+        <v>-0.7738292687656488</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.363435396965444</v>
+        <v>2.255597012061149</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532492</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.077434667613376</v>
+        <v>-5.223809780903325</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6852933108067423</v>
+        <v>0.6267432654907625</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5940986272584906</v>
+        <v>-0.7738292687656488</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.360164425810746</v>
+        <v>2.252326040906451</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793909</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.047732543637083</v>
+        <v>-5.194107656927032</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.697857552159173</v>
+        <v>0.6393075068431933</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5985687524738039</v>
+        <v>-0.7782993939809622</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.358165742443471</v>
+        <v>2.250327357539176</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011242</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.868357122398315</v>
+        <v>-5.014732235688264</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7633946959610942</v>
+        <v>0.7048446506451147</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4417919943030852</v>
+        <v>-0.6215226358102435</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.446018772652317</v>
+        <v>2.338180387748022</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982234</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.913371335918921</v>
+        <v>-5.05974644920887</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7261964658844418</v>
+        <v>0.6676464205684622</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4721408896176899</v>
+        <v>-0.6518715311248481</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.408616890795144</v>
+        <v>2.300778505890849</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509544</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.180375846191356</v>
+        <v>-5.326750959481305</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6250862241144133</v>
+        <v>0.566536178798434</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6665039276606384</v>
+        <v>-0.8462345691677966</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.29769063030832</v>
+        <v>2.189852245404025</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760819</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.281573627628529</v>
+        <v>-5.427948740918477</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5838110334360458</v>
+        <v>0.5252609881200661</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7349127412059575</v>
+        <v>-0.9146433827131157</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.25584926407763</v>
+        <v>2.148010879173335</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815461</v>
+        <v>3.705571661815465</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.249098041457756</v>
+        <v>-5.395473154747705</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5944012294586716</v>
+        <v>0.5358511841426918</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7349127412059575</v>
+        <v>-0.9146433827131157</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.253449225631947</v>
+        <v>2.145610840727652</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378106</v>
+        <v>3.709510443378109</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.230059913750459</v>
+        <v>-5.376435027040408</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5985411997498353</v>
+        <v>0.5399911544338556</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.793096352537152</v>
+        <v>-0.9728269940443103</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.215063778041475</v>
+        <v>2.10722539313718</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131256</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.261186544901078</v>
+        <v>-5.407561658191026</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7636724162282684</v>
+        <v>0.7051223709122887</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.793096352537152</v>
+        <v>-0.9728269940443103</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.392645646980156</v>
+        <v>2.284807262075861</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.722447362067875</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.313506925501869</v>
+        <v>-5.459882038791818</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7435775929740851</v>
+        <v>0.6850275476581058</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7581494925282799</v>
+        <v>-0.9378801340354381</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.414447091971613</v>
+        <v>2.306608707067318</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789129</v>
+        <v>3.787425580789132</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.333764224030827</v>
+        <v>-5.480139337320776</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7414832039594281</v>
+        <v>0.6829331586434484</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7581494925282799</v>
+        <v>-0.9378801340354381</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.420455622368539</v>
+        <v>2.312617237464244</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519913</v>
+        <v>3.781501250519916</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.186021253795825</v>
+        <v>-5.332396367085773</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8797330398454508</v>
+        <v>0.8211829945294715</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5903421352933967</v>
+        <v>-0.770072776800555</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.60029268450149</v>
+        <v>2.492454299597195</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181178</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.288035936327046</v>
+        <v>-5.434411049616995</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8417207883644435</v>
+        <v>0.7831707430484638</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5903421352933967</v>
+        <v>-0.770072776800555</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.603086306032971</v>
+        <v>2.495247921128676</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394738</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.151426592232953</v>
+        <v>-5.297801705522902</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8970268743937391</v>
+        <v>0.8384768290777593</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4537327911993043</v>
+        <v>-0.6334634327064625</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.685714260881085</v>
+        <v>2.57787587597679</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890616</v>
+        <v>3.79823979489062</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.294191925055603</v>
+        <v>-5.440567038345552</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.839001218004789</v>
+        <v>0.7804511726888097</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5964981240219547</v>
+        <v>-0.7762287655291129</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.599135537927605</v>
+        <v>2.49129715302331</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.231893926279481</v>
+        <v>-5.37826903956943</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9302559713120591</v>
+        <v>0.8717059259960793</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5964981240219547</v>
+        <v>-0.7762287655291129</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.665471091724426</v>
+        <v>2.557632706820131</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992198</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.030103728614323</v>
+        <v>-5.176478841904272</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7195529227675199</v>
+        <v>0.6610028774515406</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3984799318528003</v>
+        <v>-0.5782105733599585</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.492862879415317</v>
+        <v>2.385024494511022</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852431</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.97021304697173</v>
+        <v>-5.116588160261679</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8137994277467326</v>
+        <v>0.7552493824307529</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3385892502102068</v>
+        <v>-0.518319891717365</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.599087520723048</v>
+        <v>2.491249135818753</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319554</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.067953591596704</v>
+        <v>-5.214328704886653</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7893309460127864</v>
+        <v>0.7307809006968071</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.354478528343187</v>
+        <v>-0.5342091698503453</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.604181689959304</v>
+        <v>2.496343305055008</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489392</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.244291351719633</v>
+        <v>-5.390666465009582</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7173318227882866</v>
+        <v>0.6587817774723068</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5308162884661164</v>
+        <v>-0.7105469299732747</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.496915014710217</v>
+        <v>2.389076629805923</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397801</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.24360197955841</v>
+        <v>-5.389977092848359</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7160991896927045</v>
+        <v>0.6575491443767247</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5308162884661164</v>
+        <v>-0.7105469299732747</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.495406632750146</v>
+        <v>2.387568247845851</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.83602339102497</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.250172944613003</v>
+        <v>-5.396548057902952</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7133336711063034</v>
+        <v>0.6547836257903237</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5373872535207094</v>
+        <v>-0.7171178950278676</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.491326921152826</v>
+        <v>2.383488536248532</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863229</v>
+        <v>3.821591150863233</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.242218974318231</v>
+        <v>-5.38859408760818</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7165152592242121</v>
+        <v>0.6579652139082328</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5373872535207094</v>
+        <v>-0.7171178950278676</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.491326921152826</v>
+        <v>2.383488536248532</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947588</v>
+        <v>3.833040181947592</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.231845597985144</v>
+        <v>-5.378220711275093</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7270463667852516</v>
+        <v>0.6684963214692723</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.527013877187622</v>
+        <v>-0.7067445186947803</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.503932703980484</v>
+        <v>2.396094319076189</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326881</v>
+        <v>3.822707244326884</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.104161288190848</v>
+        <v>-5.250536401480796</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7830124640776952</v>
+        <v>0.7244624187617155</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3993295673933256</v>
+        <v>-0.5790602089004838</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.585435663231786</v>
+        <v>2.477597278327491</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314556</v>
+        <v>3.82883791131456</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.164827878593236</v>
+        <v>-5.311202991883185</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7455005003926116</v>
+        <v>0.6869504550766323</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.4810278841118593</v>
+        <v>-0.6607585256190175</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.523171345676538</v>
+        <v>2.415332960772243</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690031</v>
+        <v>3.816866067690035</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.099834018659591</v>
+        <v>-5.24620913194954</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7755957469766988</v>
+        <v>0.717045701660719</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4541972695077039</v>
+        <v>-0.6339279110148621</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.54336741704966</v>
+        <v>2.435529032145365</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674314</v>
+        <v>3.817961388674318</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.200592654416589</v>
+        <v>-5.346967767706538</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7394532323049772</v>
+        <v>0.6809031869889979</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5430228382347093</v>
+        <v>-0.7227534797418675</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.494233015444535</v>
+        <v>2.38639463054024</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163224</v>
+        <v>3.826713779163227</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.156389817330688</v>
+        <v>-5.302764930620637</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7630139696671745</v>
+        <v>0.7044639243511952</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.4988200011488089</v>
+        <v>-0.6785506426559671</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.526634320223912</v>
+        <v>2.418795935319617</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022909</v>
+        <v>3.838228663022912</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.193368844994131</v>
+        <v>-5.33974395828408</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7466323590710453</v>
+        <v>0.6880823137550656</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4618460993574783</v>
+        <v>-0.6415767408646366</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.547228661767958</v>
+        <v>2.439390276863663</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042143</v>
+        <v>3.863924114042146</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.213426923858972</v>
+        <v>-5.359802037148921</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7898568927081486</v>
+        <v>0.7313068473921689</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4618460993574783</v>
+        <v>-0.6415767408646366</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.598476426950998</v>
+        <v>2.490638042046703</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,45 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.825841490223261</v>
+        <v>3.86536771507829</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.173496250681081</v>
+        <v>-5.31987136397103</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8042698665735579</v>
+        <v>0.7457198212575782</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.421915426179588</v>
+        <v>-0.6016460676867462</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.620875535451985</v>
+        <v>2.51303715054769</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="2" t="n">
+        <v>45449</v>
+      </c>
+      <c r="B1987" t="n">
+        <v>3.750406560961471</v>
+      </c>
+      <c r="C1987" t="n">
+        <v>2.777471567898657</v>
+      </c>
+      <c r="D1987" t="n">
+        <v>-5.31987136397103</v>
+      </c>
+      <c r="E1987" t="n">
+        <v>0.7457198212575782</v>
+      </c>
+      <c r="F1987" t="n">
+        <v>-0.6016460676867462</v>
+      </c>
+      <c r="G1987" t="n">
+        <v>2.770535364885025</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240606.xlsx
+++ b/tame_output/ON/bt/strategyON_20240606.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,45 +791,45 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.0%</t>
+          <t>-81.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>129.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-704.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-52.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.8%</t>
+          <t>453.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-693.6%</t>
+          <t>-698.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-282.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-301.7%</t>
+          <t>-271.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.1%</t>
+          <t>-308.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.0%</t>
+          <t>-154.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-284.2%</t>
+          <t>-280.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.1%</t>
+          <t>-185.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.0%</t>
+          <t>-128.4%</t>
         </is>
       </c>
     </row>
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.310015937072177</v>
+        <v>-5.424892646946397</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9879935098902566</v>
+        <v>0.9420428259405687</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.844571510757425</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.619581299605434</v>
+        <v>2.60561340257842</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.64567858430263</v>
+        <v>-5.760555294176849</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8523090426540407</v>
+        <v>0.8063583587043528</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.844571510757425</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.618161891261399</v>
+        <v>2.604193994234385</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.009304829202943</v>
+        <v>-6.124181539077163</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7133461049281569</v>
+        <v>0.6673954209784689</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9195133192461942</v>
+        <v>-0.9427931476245508</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.565716469375365</v>
+        <v>2.551748572348351</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.489308921715909</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.5205989829288016</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.215824103545207</v>
+        <v>-1.239103931923563</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.387184513801789</v>
+        <v>2.373216616774775</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.897897698896587</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.3559250160712892</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.647692709104242</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.140792791508141</v>
+        <v>2.126824894481127</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-7.17447379921242</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.2404800084164171</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.647692709104242</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.135978223979602</v>
+        <v>2.122010326952588</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.590865673499417</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.07191730931049545</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.647692709104242</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.133972274588479</v>
+        <v>2.120004377561465</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.792600906165847</v>
+        <v>-7.907477616040065</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.001481906912602859</v>
+        <v>-0.04446877703708463</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.647692709104242</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.144230965257158</v>
+        <v>2.130263068230144</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.138475728150656</v>
+        <v>-8.253352438024875</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1407684567356258</v>
+        <v>-0.1867191406853133</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.647692709104242</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.140330530402853</v>
+        <v>2.126362633375839</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.30205560633504</v>
+        <v>-8.416932316209259</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2077954879543786</v>
+        <v>-0.2537461719040661</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.647692709104242</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.138735450457854</v>
+        <v>2.12476755343084</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.598716948145238</v>
+        <v>-8.713593658019457</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3226810487492497</v>
+        <v>-0.3686317326989372</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.71643584483812</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.087300647919721</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.803748128919555</v>
+        <v>-8.918624838793773</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4087198255933795</v>
+        <v>-0.454670509543067</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.71643584483812</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.083274343385318</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.186749517662186</v>
+        <v>-9.301626227536405</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5620224824120159</v>
+        <v>-0.6079731663617034</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.71643584483812</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.083172242063734</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.36861930864722</v>
+        <v>-9.483496018521439</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6321988828345995</v>
+        <v>-0.678149566784287</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.898305635823155</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>1.976621883444143</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.728149631151222</v>
+        <v>-9.843026341025441</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7706607085381503</v>
+        <v>-0.8166113924878378</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.898305635823155</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>1.981972186742193</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.778498694605444</v>
+        <v>-9.893375404479663</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7828843139626613</v>
+        <v>-0.8288349979123488</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.948654699277377</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>1.959678768626838</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.87611797202684</v>
+        <v>-9.990994681901059</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8188902743094508</v>
+        <v>-0.8648409582591383</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-2.046273976698774</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.904148952795768</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.02364406003248</v>
+        <v>-10.1385207699067</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8750071531901358</v>
+        <v>-0.9209578371398233</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.193800064704418</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.818526856313954</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.22790223536235</v>
+        <v>-10.34277894523657</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9511972262034387</v>
+        <v>-0.9971479101531262</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.321439009318407</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.747456686664203</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.36971200956913</v>
+        <v>-10.48458871944335</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.003438581401718</v>
+        <v>-1.049389265351406</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.492717806963982</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.649171962561294</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.29624217790169</v>
+        <v>-10.4111188877759</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9586789472413173</v>
+        <v>-1.004629631191005</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.419247975296534</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.708625563055184</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.47136659528823</v>
+        <v>-10.58624330516245</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.014173493448418</v>
+        <v>-1.060124177398105</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.594372392683078</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.618106133370775</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.70581868930272</v>
+        <v>-10.82069539917694</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.11517349595581</v>
+        <v>-1.161124179905497</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.594372392683078</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.610886968469179</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764399</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.99362253383996</v>
+        <v>-11.10849924371418</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.236967224544682</v>
+        <v>-1.282917908494369</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.882176237220316</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.43153247097286</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.04640868944028</v>
+        <v>-11.1612853993145</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.256965896946256</v>
+        <v>-1.302916580895944</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.977851723802713</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.375242968861978</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.17244548280857</v>
+        <v>-11.28732219268279</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.304686885664457</v>
+        <v>-1.350637569614145</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.95260010099297</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.393087671176938</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.12042996883976</v>
+        <v>-11.23530667871398</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.279890344390531</v>
+        <v>-1.325841028340219</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.95260010099297</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.397078006863339</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.26210181056388</v>
+        <v>-11.3769785204381</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.338034307978921</v>
+        <v>-1.383984991928608</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.95260010099297</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.395602779964597</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.21251096613905</v>
+        <v>-11.32738767601326</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.303144560044114</v>
+        <v>-1.349095243993802</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.903009256568136</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.44041069678437</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.19970357313427</v>
+        <v>-11.31458028300849</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.311072736488888</v>
+        <v>-1.357023420438576</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.951865031577037</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.398046098132346</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.97385842041486</v>
+        <v>-11.08873513028908</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.211155602364915</v>
+        <v>-1.257106286314603</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.909938355989873</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.432781176520853</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.84927976407727</v>
+        <v>-10.96415647395149</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.160184995273819</v>
+        <v>-1.206135679223507</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.909938355989873</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.433920321076912</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.90217505212155</v>
+        <v>-11.01705176199578</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.178709336329426</v>
+        <v>-1.224660020279114</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.904983009901427</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.439527302892087</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83004187683367</v>
+        <v>-10.94491858670789</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.144122361975637</v>
+        <v>-1.190073045925325</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.904983009901427</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.445261007130724</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955331</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.81868753622064</v>
+        <v>-10.87355219409825</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.149317888124288</v>
+        <v>-1.171263751275331</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.870348840910036</v>
+        <v>-2.833616617291779</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.456304246131694</v>
+        <v>1.478343580302647</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232415</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.55485066901657</v>
+        <v>-10.60971532689418</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.053666622555567</v>
+        <v>-1.075612485706611</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.870348840910036</v>
+        <v>-2.833616617291779</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.446420764818786</v>
+        <v>1.46846009898974</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436231</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.28760886814817</v>
+        <v>-10.34247352602578</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9486044627075825</v>
+        <v>-0.9705503258586261</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.870348840910036</v>
+        <v>-2.833616617291779</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.444586204319412</v>
+        <v>1.466625538490366</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.18970182947168</v>
+        <v>-10.24456648734929</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9097419622104472</v>
+        <v>-0.93168782536149</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.802363091049479</v>
+        <v>-2.765630867431223</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.485077339262285</v>
+        <v>1.507116673433239</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.16574828849572</v>
+        <v>-10.22061294637333</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8994920396745703</v>
+        <v>-0.9214379028256139</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.778409550073522</v>
+        <v>-2.741677326455265</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.500117969993353</v>
+        <v>1.522157304164307</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017774</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.901688350172925</v>
+        <v>-9.956553008050534</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8071283805072036</v>
+        <v>-0.8290742436582468</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.514349611750725</v>
+        <v>-2.477617388132469</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.645293616825279</v>
+        <v>1.667332950996233</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839729</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.194608726668088</v>
+        <v>-9.249473384545697</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5270835647655696</v>
+        <v>-0.5490294279166128</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.514349611750725</v>
+        <v>-2.477617388132469</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.642506583164978</v>
+        <v>1.664545917335932</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388732</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.154424428301898</v>
+        <v>-9.209289086179506</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5106662215312521</v>
+        <v>-0.5326120846822953</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.474165313384534</v>
+        <v>-2.437433089766278</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.666960786072534</v>
+        <v>1.689000120243488</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626478</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.074354632764093</v>
+        <v>-9.129219290641702</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4792714820953732</v>
+        <v>-0.5012173452464168</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.39409551784673</v>
+        <v>-2.357363294228474</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.714369484615973</v>
+        <v>1.736408818786927</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291816</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.840873410534495</v>
+        <v>-8.895738068412104</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3779545643656816</v>
+        <v>-0.3999004275167253</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.160614295617132</v>
+        <v>-2.123882071998876</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.862382646791585</v>
+        <v>1.884421980962539</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.691207019526981</v>
+        <v>-8.74607167740459</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3209802182756354</v>
+        <v>-0.3429260814266786</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.067710804374596</v>
+        <v>-2.03097858075634</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.915232531224148</v>
+        <v>1.937271865395101</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.558931545896094</v>
+        <v>-8.613796203773703</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2727025420762534</v>
+        <v>-0.2946484052272966</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.935435330743709</v>
+        <v>-1.898703107125453</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.989965302149707</v>
+        <v>2.01200463632066</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105958</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.36833187122294</v>
+        <v>-8.423196529100549</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1936476115193551</v>
+        <v>-0.2155934746703987</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.744835656070556</v>
+        <v>-1.7081034324523</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.107140167641235</v>
+        <v>2.129179501812189</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.119332072539359</v>
+        <v>-8.174196730416968</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.08114135082226381</v>
+        <v>-0.1030872139733074</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.744835656070556</v>
+        <v>-1.7081034324523</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.120046508864894</v>
+        <v>2.142085843035847</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.224922062312464</v>
+        <v>-8.279786720190073</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2513532763307245</v>
+        <v>-0.2732991394817681</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.850425645843661</v>
+        <v>-1.813693422225404</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.928716585401812</v>
+        <v>1.950755919572766</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987909</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.243656964431061</v>
+        <v>-8.29852162230867</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2103028953010768</v>
+        <v>-0.2322487584521205</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.856021655503792</v>
+        <v>-1.819289431885536</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.97390332148282</v>
+        <v>1.995942655653773</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.095716923023462</v>
+        <v>-8.15058158090107</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2710058014262047</v>
+        <v>-0.2929516645772483</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.835700739595234</v>
+        <v>-1.798968515976978</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.866216948339787</v>
+        <v>1.888256282510741</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409212</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.078558772892167</v>
+        <v>-8.133423430769776</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2728565276271651</v>
+        <v>-0.2948023907782087</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.81854258946394</v>
+        <v>-1.781810365845684</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.867797852165085</v>
+        <v>1.889837186336039</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098116</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.035010366121476</v>
+        <v>-8.089875023999085</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.262397777013982</v>
+        <v>-0.2843436401650252</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.81854258946394</v>
+        <v>-1.781810365845684</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.860837240069992</v>
+        <v>1.882876574240946</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.792861972667618</v>
+        <v>-7.847726630545226</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1510760652512957</v>
+        <v>-0.1730219284023389</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.81854258946394</v>
+        <v>-1.781810365845684</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.875299594451135</v>
+        <v>1.897338928622089</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722823</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.684602835545096</v>
+        <v>-7.739467493422705</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.113240289943092</v>
+        <v>-0.1351861530941352</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.81854258946394</v>
+        <v>-1.781810365845684</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.86983171491033</v>
+        <v>1.891871049081284</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792053</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.561311700727965</v>
+        <v>-7.616176358605574</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.06642574200566242</v>
+        <v>-0.08837160515670606</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.695251454646809</v>
+        <v>-1.658519231028553</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.941304489811186</v>
+        <v>1.963343823982139</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919914</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.540162501824522</v>
+        <v>-7.595027159702131</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.05026508420696008</v>
+        <v>-0.07221094735800371</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.674102255743366</v>
+        <v>-1.63737003212511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.961694987390577</v>
+        <v>1.98373432156153</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318099</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.296397059841078</v>
+        <v>-7.351261717718686</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.04302180093346841</v>
+        <v>0.02107593778242478</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.674102255743366</v>
+        <v>-1.63737003212511</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.957475695737628</v>
+        <v>1.979515029908581</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057532</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.194634239563783</v>
+        <v>-7.249498897441391</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.08585124296440227</v>
+        <v>0.06390537981335864</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.660883187350937</v>
+        <v>-1.624150963732681</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.967531450693101</v>
+        <v>1.989570784864054</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279192</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.944783845614708</v>
+        <v>-6.999648503492317</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1785334755277344</v>
+        <v>0.1565876123766907</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.660883187350937</v>
+        <v>-1.624150963732681</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.960273525676803</v>
+        <v>1.982312859847756</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011505</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.768891753147276</v>
+        <v>-6.823756411024885</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.252489436035356</v>
+        <v>0.2305435728843124</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.660883187350937</v>
+        <v>-1.624150963732681</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.963872649197452</v>
+        <v>1.985911983368405</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392994</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.597445290124813</v>
+        <v>-6.652309948002421</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.334395527298895</v>
+        <v>0.3124496641478514</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.489436724328474</v>
+        <v>-1.452704500710218</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.080068033065483</v>
+        <v>2.102107367236437</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632789</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.37241229045599</v>
+        <v>-6.427276948333598</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4234292047827211</v>
+        <v>0.4014833416316774</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.264403724659651</v>
+        <v>-1.227671501041395</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.214108310483074</v>
+        <v>2.236147644654028</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.308776548222055</v>
+        <v>-6.363641206099664</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4535783027306119</v>
+        <v>0.4316324395795688</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.200767982425717</v>
+        <v>-1.164035758807461</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.256984556877752</v>
+        <v>2.279023891048706</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.215776507016157</v>
+        <v>-6.270641164893766</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.471972577996767</v>
+        <v>0.4500267148457238</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.200767982425717</v>
+        <v>-1.164035758807461</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.238178815661548</v>
+        <v>2.260218149832501</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242299</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.975346010211297</v>
+        <v>-6.030210668088905</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5698878533435887</v>
+        <v>0.5479419901925451</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9603374856208564</v>
+        <v>-0.9236052620026003</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.384180190369341</v>
+        <v>2.406219524540295</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367689</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.903103442040102</v>
+        <v>-5.957968099917711</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6027141944468868</v>
+        <v>0.5807683312958432</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9603374856208564</v>
+        <v>-0.9236052620026003</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.388109504204161</v>
+        <v>2.410148838375115</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879968</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.850105119758714</v>
+        <v>-5.904969777636323</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6245921072767819</v>
+        <v>0.6026462441257383</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9050012266189176</v>
+        <v>-0.8682690030006615</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.421989843522665</v>
+        <v>2.444029177693618</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.848616626502342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.741300234278987</v>
+        <v>-5.796164892156596</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.665112132688666</v>
+        <v>0.6431662695376228</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9050012266189176</v>
+        <v>-0.8682690030006615</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.418987914742658</v>
+        <v>2.441027248913612</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675944</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.521279436241977</v>
+        <v>-5.576144094119585</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7546994889140843</v>
+        <v>0.7327536257630411</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7637813815509373</v>
+        <v>-0.7270491579326812</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.505298858794061</v>
+        <v>2.527338192965014</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.388411747178699</v>
+        <v>-5.443276405056308</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.823740747341219</v>
+        <v>0.8017948841901754</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7637813815509373</v>
+        <v>-0.7270491579326812</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.521193041595883</v>
+        <v>2.543232375766837</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496268</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.228896643659329</v>
+        <v>-5.283761301536938</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8886926331892688</v>
+        <v>0.8667467700382252</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6042662780315674</v>
+        <v>-0.5675340544133113</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.618047948147808</v>
+        <v>2.640087282318761</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577005</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.084224498559592</v>
+        <v>-5.1390891564372</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9566495937906034</v>
+        <v>0.9347037306395602</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.45959413293183</v>
+        <v>-0.4228619093135739</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.71493933776909</v>
+        <v>2.736978671940043</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.73583922294211</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.144099325917284</v>
+        <v>-5.198963983794893</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9187371542489524</v>
+        <v>0.8967912910979088</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5194689602895222</v>
+        <v>-0.482736736671266</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.6650519327559</v>
+        <v>2.687091266926854</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674522</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.057299828138275</v>
+        <v>-5.112164486015883</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.975857446683122</v>
+        <v>0.9539115835320788</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5194689602895222</v>
+        <v>-0.482736736671266</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.687452426078466</v>
+        <v>2.70949176024942</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430701</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.059769534600081</v>
+        <v>-5.114634192477689</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9749419654718121</v>
+        <v>0.9529961023207685</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5219386667513284</v>
+        <v>-0.4852064431330722</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.686043003574795</v>
+        <v>2.708082337745748</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003609</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.128139720924091</v>
+        <v>-5.1830043788017</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9586008134169099</v>
+        <v>0.9366549502658663</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5126629677151134</v>
+        <v>-0.4759307440968572</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.702615345471226</v>
+        <v>2.72465467964218</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508378</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.236677901840225</v>
+        <v>-5.291542559717834</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9056222496823474</v>
+        <v>0.8836763865313042</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5126629677151134</v>
+        <v>-0.4759307440968572</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.693052054103117</v>
+        <v>2.715091388274071</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.71090673141771</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>3.149557317538017</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.26767106116893</v>
+        <v>-5.314362255229757</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7179345509912523</v>
+        <v>1.023455991132367</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5126629677151134</v>
+        <v>-0.4759307440968572</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.517761619143504</v>
+        <v>2.863998871079903</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>3.154124549529805</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.092196801376462</v>
+        <v>-5.138887995437289</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7926914869000274</v>
+        <v>1.098212927041142</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5126629677151134</v>
+        <v>-0.4759307440968572</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.522328851135291</v>
+        <v>2.868566103071691</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>3.129866578291012</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.203133054017711</v>
+        <v>-5.249824248078538</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7240590146047352</v>
+        <v>1.02958045474585</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5126629677151134</v>
+        <v>-0.4759307440968572</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.498070879896499</v>
+        <v>2.844308131832898</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111302</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>3.132997963510918</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.406159631560944</v>
+        <v>-5.452850825621771</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6459797688073472</v>
+        <v>0.951501208948462</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7156895452583468</v>
+        <v>-0.6789573216400906</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.379386318590464</v>
+        <v>2.725623570526864</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>3.14317034994305</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.248234032625651</v>
+        <v>-5.294925226686478</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7193223948135969</v>
+        <v>1.024843834954712</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7156895452583468</v>
+        <v>-0.6789573216400906</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.389558705022597</v>
+        <v>2.735795956958996</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742307</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>3.13811662051691</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.161990569599273</v>
+        <v>-5.2086817636601</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7487660505980083</v>
+        <v>1.054287490739123</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7156895452583468</v>
+        <v>-0.6789573216400906</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.384504975596457</v>
+        <v>2.730742227532856</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316054</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>3.129892395961436</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.207297388998253</v>
+        <v>-5.25398858305908</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7224190982829417</v>
+        <v>1.027940538424057</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7564997082675776</v>
+        <v>-0.7197674846493214</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.351794653235444</v>
+        <v>2.698031905171844</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803199</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>3.130444268994538</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.236330493700554</v>
+        <v>-5.283021687761381</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.711357729435123</v>
+        <v>1.016879169576238</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7564997082675776</v>
+        <v>-0.7197674846493214</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.352346526268545</v>
+        <v>2.698583778204945</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809505</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>3.059716960885903</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.143520012249694</v>
+        <v>-5.190211206310521</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6777546139068327</v>
+        <v>0.9832760540479475</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6636892268167183</v>
+        <v>-0.626957003198462</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.337305507030427</v>
+        <v>2.683542758966826</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>3.061590436810504</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.187909481579122</v>
+        <v>-5.234600675639949</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6618723020996624</v>
+        <v>0.9673937422407772</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7080786961461459</v>
+        <v>-0.6713464725278897</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.312545301357371</v>
+        <v>2.65878255329377</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472745</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>3.056666145322227</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.075238263342872</v>
+        <v>-5.121929457403699</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7020164979058854</v>
+        <v>1.007537938047</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5954074779098957</v>
+        <v>-0.5586752542916396</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.375223740810844</v>
+        <v>2.721460992747244</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798544</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>3.062157441152894</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.962861262160199</v>
+        <v>-5.009552456221026</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7524585942096218</v>
+        <v>1.057980034350737</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5954074779098957</v>
+        <v>-0.5586752542916396</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.380715036641512</v>
+        <v>2.726952288577911</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498872</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>3.073654642921433</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.161095831046929</v>
+        <v>-5.207787025107756</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6846619684234687</v>
+        <v>0.9901834085645835</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7936420467966263</v>
+        <v>-0.7569098231783702</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.273271497078012</v>
+        <v>2.619508749014412</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705332</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.912010362922087</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.244097112072208</v>
+        <v>-5.290788306133035</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4898171760140104</v>
+        <v>0.7953386161551252</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.8122129313238</v>
+        <v>-0.7754807077055439</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.100484686362361</v>
+        <v>2.446721938298761</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729277</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>3.032160023641292</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.35271119051554</v>
+        <v>-5.399402384576367</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5665212053558832</v>
+        <v>0.8720426454969985</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.8122129313238</v>
+        <v>-0.7754807077055439</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.220634347081567</v>
+        <v>2.566871599017966</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190777</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>3.046673049743615</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.439309773496642</v>
+        <v>-5.486000967557469</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5463947982657653</v>
+        <v>0.8519162384068801</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.8122129313238</v>
+        <v>-0.7754807077055439</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.23514737318389</v>
+        <v>2.581384625120289</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913432</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>3.044092491085984</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.400926110938491</v>
+        <v>-5.533669797223982</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5591677046313945</v>
+        <v>0.8302681478826441</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7738292687656488</v>
+        <v>-0.8231495373720561</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.255597012061149</v>
+        <v>2.55020276866275</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532492</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>3.040821519931286</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.223809780903325</v>
+        <v>-5.356553467188816</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6267432654907625</v>
+        <v>0.8978437087420121</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7738292687656488</v>
+        <v>-0.8231495373720561</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.252326040906451</v>
+        <v>2.546931797508052</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793909</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>3.041504911693199</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.194107656927032</v>
+        <v>-5.326851343212522</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6393075068431933</v>
+        <v>0.9104079500944429</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7782993939809622</v>
+        <v>-0.8276196625873695</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.250327357539176</v>
+        <v>2.544933114140778</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011242</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>3.035291886999613</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.014732235688264</v>
+        <v>-5.147475921973754</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7048446506451147</v>
+        <v>0.9759450938963643</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6215226358102435</v>
+        <v>-0.6708429044166508</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.338180387748022</v>
+        <v>2.632786144349623</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982237</v>
+        <v>3.716991718982235</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>3.016099342331203</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.05974644920887</v>
+        <v>-5.19249013549436</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6676464205684622</v>
+        <v>0.9387468638197118</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6518715311248481</v>
+        <v>-0.7011917997312554</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.300778505890849</v>
+        <v>2.59538426249245</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509544</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>3.021790904670149</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.326750959481305</v>
+        <v>-5.459494645766795</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.566536178798434</v>
+        <v>0.8376366220496836</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8462345691677966</v>
+        <v>-0.895554837774204</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.189852245404025</v>
+        <v>2.484458002005627</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760819</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>3.02099482656665</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.427948740918477</v>
+        <v>-5.560692427203968</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5252609881200661</v>
+        <v>0.7963614313713157</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9146433827131157</v>
+        <v>-0.9639636513195231</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.148010879173335</v>
+        <v>2.442616635774937</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815465</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>3.018594788120967</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.395473154747705</v>
+        <v>-5.528216841033196</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5358511841426918</v>
+        <v>0.8069516273939414</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9146433827131157</v>
+        <v>-0.9639636513195231</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.145610840727652</v>
+        <v>2.440216597329253</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378109</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>3.015119507329212</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.376435027040408</v>
+        <v>-5.509178713325898</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5399911544338556</v>
+        <v>0.8110915976851052</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9728269940443103</v>
+        <v>-1.022147262650718</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.10722539313718</v>
+        <v>2.401831149738782</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>3.192701376267892</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.407561658191026</v>
+        <v>-5.540305344476517</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7051223709122887</v>
+        <v>0.9762228141635383</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9728269940443103</v>
+        <v>-1.022147262650718</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.284807262075861</v>
+        <v>2.579413018677462</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>3.193534705254026</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.459882038791818</v>
+        <v>-5.592625725077308</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6850275476581058</v>
+        <v>0.9561279909093554</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9378801340354381</v>
+        <v>-0.9872004026418454</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.306608707067318</v>
+        <v>2.601214463668919</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789132</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>3.199543235650952</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.480139337320776</v>
+        <v>-5.612883023606266</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6829331586434484</v>
+        <v>0.954033601894698</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9378801340354381</v>
+        <v>-0.9872004026418454</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.312617237464244</v>
+        <v>2.607222994065845</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519916</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.278695883442974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.332396367085773</v>
+        <v>-5.465140053371264</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8211829945294715</v>
+        <v>1.092283437780721</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.770072776800555</v>
+        <v>-0.8193930454069622</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.492454299597195</v>
+        <v>2.787060056198797</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181178</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.281489504974455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.434411049616995</v>
+        <v>-5.567154735902485</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7831707430484638</v>
+        <v>1.054271186299713</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.770072776800555</v>
+        <v>-0.8193930454069622</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.495247921128676</v>
+        <v>2.789853677730278</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394738</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.282151853366113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.297801705522902</v>
+        <v>-5.430545391808392</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8384768290777593</v>
+        <v>1.109577272329009</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6334634327064625</v>
+        <v>-0.6827837013128697</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.57787587597679</v>
+        <v>2.872481632578392</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489062</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.281232330106223</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.440567038345552</v>
+        <v>-5.573310724631042</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7804511726888097</v>
+        <v>1.051551615940059</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7762287655291129</v>
+        <v>-0.8255490341355201</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.49129715302331</v>
+        <v>2.785902909624911</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.347567883903044</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.37826903956943</v>
+        <v>-5.51101272585492</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8717059259960793</v>
+        <v>1.142806369247329</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7762287655291129</v>
+        <v>-0.8255490341355201</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.557632706820131</v>
+        <v>2.852238463421732</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992198</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>3.056148756292442</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.176478841904272</v>
+        <v>-5.309222528189762</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6610028774515406</v>
+        <v>0.9321033207027902</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5782105733599585</v>
+        <v>-0.6275308419663657</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.385024494511022</v>
+        <v>2.679630251112623</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>3.126438988614618</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.116588160261679</v>
+        <v>-5.249331846547169</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7552493824307529</v>
+        <v>1.026349825682003</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.518319891717365</v>
+        <v>-0.5676401603237722</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.491249135818753</v>
+        <v>2.785854892420355</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319554</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>3.141066724730661</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.214328704886653</v>
+        <v>-5.347072391172143</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7307809006968071</v>
+        <v>1.001881343948057</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5342091698503453</v>
+        <v>-0.5835294384567524</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.496343305055008</v>
+        <v>2.79094906165661</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489392</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>3.139602705555333</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.390666465009582</v>
+        <v>-5.523410151295073</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6587817774723068</v>
+        <v>0.9298822207235564</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7105469299732747</v>
+        <v>-0.7598671985796819</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.389076629805923</v>
+        <v>2.683682386407524</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397801</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>3.138094323595261</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.389977092848359</v>
+        <v>-5.52272077913385</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6575491443767247</v>
+        <v>0.9286495876279743</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7105469299732747</v>
+        <v>-0.7598671985796819</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.387568247845851</v>
+        <v>2.682174004447452</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102497</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>3.137957191030698</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.396548057902952</v>
+        <v>-5.529291744188442</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6547836257903237</v>
+        <v>0.9258840690415733</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7171178950278676</v>
+        <v>-0.7664381636342747</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.383488536248532</v>
+        <v>2.678094292850133</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863233</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>3.137957191030698</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.38859408760818</v>
+        <v>-5.52133777389367</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6579652139082328</v>
+        <v>0.9290656571594824</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7171178950278676</v>
+        <v>-0.7664381636342747</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.383488536248532</v>
+        <v>2.678094292850133</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947592</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>3.144338948058502</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.378220711275093</v>
+        <v>-5.510964397560583</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6684963214692723</v>
+        <v>0.9395967647205219</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7067445186947803</v>
+        <v>-0.7560647873011874</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.396094319076189</v>
+        <v>2.69070007567779</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326884</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>3.149231321433227</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.250536401480796</v>
+        <v>-5.383280087766287</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7244624187617155</v>
+        <v>0.9955628620129651</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5790602089004838</v>
+        <v>-0.628380477506891</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.477597278327491</v>
+        <v>2.772203034929093</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82883791131456</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>3.135985993909099</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.311202991883185</v>
+        <v>-5.443946678168675</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6869504550766323</v>
+        <v>0.9580508983278819</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6607585256190175</v>
+        <v>-0.7100787942254246</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.415332960772243</v>
+        <v>2.709938717373845</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690035</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>3.140083696519728</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.24620913194954</v>
+        <v>-5.37895281823503</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.717045701660719</v>
+        <v>0.9881461449119686</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6339279110148621</v>
+        <v>-0.6832481796212693</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.435529032145365</v>
+        <v>2.730134788746966</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674318</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>3.144244636150806</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.346967767706538</v>
+        <v>-5.479711453992028</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6809031869889979</v>
+        <v>0.9520036302402475</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7227534797418675</v>
+        <v>-0.7720737483482747</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.38639463054024</v>
+        <v>2.681000387141841</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163227</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>3.150124238678643</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.302764930620637</v>
+        <v>-5.435508616906128</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7044639243511952</v>
+        <v>0.9755643676024448</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6785506426559671</v>
+        <v>-0.7278709112623742</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.418795935319617</v>
+        <v>2.713401691921219</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022912</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>3.148534239147891</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.33974395828408</v>
+        <v>-5.47248764456957</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6880823137550656</v>
+        <v>0.9591827570063152</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6415767408646366</v>
+        <v>-0.6908970094710437</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.439390276863663</v>
+        <v>2.733996033465265</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042146</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>3.19978200433093</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.359802037148921</v>
+        <v>-5.492545723434411</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7313068473921689</v>
+        <v>1.002407290643418</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6415767408646366</v>
+        <v>-0.6908970094710437</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.490638042046703</v>
+        <v>2.785243798648304</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507829</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>3.198222708925183</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.31987136397103</v>
+        <v>-5.37084192364795</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7457198212575782</v>
+        <v>1.049529515152256</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.6016460676867462</v>
+        <v>-0.5691932096845825</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.51303715054769</v>
+        <v>2.856706783114434</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.750406560961471</v>
+        <v>3.762257370250698</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.777471567898657</v>
+        <v>3.182797099657121</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.31987136397103</v>
+        <v>-5.37084192364795</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7457198212575782</v>
+        <v>1.049529515152256</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.6016460676867462</v>
+        <v>-0.5691932096845825</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.770535364885025</v>
+        <v>3.175860896643488</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240606.xlsx
+++ b/tame_output/ON/bt/strategyON_20240606.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,55 +791,55 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>-25.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.3%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.2%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-704.1%</t>
+          <t>-692.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.8%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-698.7%</t>
+          <t>-686.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-282.0%</t>
+          <t>-277.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-42.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-271.3%</t>
+          <t>-298.9%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-308.4%</t>
+          <t>-306.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.2%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-280.9%</t>
+          <t>-278.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-185.5%</t>
+          <t>-184.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-128.4%</t>
+          <t>-160.9%</t>
         </is>
       </c>
     </row>
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.424892646946397</v>
+        <v>-5.310015937072177</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9420428259405687</v>
+        <v>0.9879935098902566</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.844571510757425</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60561340257842</v>
+        <v>2.619581299605434</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.760555294176849</v>
+        <v>-5.64567858430263</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8063583587043528</v>
+        <v>0.8523090426540407</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.844571510757425</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.604193994234385</v>
+        <v>2.618161891261399</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.124181539077163</v>
+        <v>-6.009304829202943</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6673954209784689</v>
+        <v>0.7133461049281569</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9427931476245508</v>
+        <v>-0.9195133192461942</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.551748572348351</v>
+        <v>2.565716469375365</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.489308921715909</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5205989829288016</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.239103931923563</v>
+        <v>-1.215824103545207</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.373216616774775</v>
+        <v>2.387184513801789</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.897897698896587</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3559250160712892</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.647692709104242</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.126824894481127</v>
+        <v>2.140792791508141</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.17447379921242</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2404800084164171</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.647692709104242</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.122010326952588</v>
+        <v>2.135978223979602</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.590865673499417</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.07191730931049545</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.647692709104242</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.120004377561465</v>
+        <v>2.133972274588479</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.907477616040065</v>
+        <v>-7.792600906165847</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.04446877703708463</v>
+        <v>0.001481906912602859</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.647692709104242</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.130263068230144</v>
+        <v>2.144230965257158</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.253352438024875</v>
+        <v>-8.138475728150656</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1867191406853133</v>
+        <v>-0.1407684567356258</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.647692709104242</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.126362633375839</v>
+        <v>2.140330530402853</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.416932316209259</v>
+        <v>-8.30205560633504</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2537461719040661</v>
+        <v>-0.2077954879543786</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.647692709104242</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.12476755343084</v>
+        <v>2.138735450457854</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.713593658019457</v>
+        <v>-8.598716948145238</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3686317326989372</v>
+        <v>-0.3226810487492497</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.71643584483812</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.087300647919721</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.918624838793773</v>
+        <v>-8.803748128919555</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.454670509543067</v>
+        <v>-0.4087198255933795</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.71643584483812</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.083274343385318</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.301626227536405</v>
+        <v>-9.186749517662186</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6079731663617034</v>
+        <v>-0.5620224824120159</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.71643584483812</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.083172242063734</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.483496018521439</v>
+        <v>-9.36861930864722</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.678149566784287</v>
+        <v>-0.6321988828345995</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.898305635823155</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.976621883444143</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.843026341025441</v>
+        <v>-9.728149631151222</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8166113924878378</v>
+        <v>-0.7706607085381503</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.898305635823155</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.981972186742193</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.893375404479663</v>
+        <v>-9.778498694605444</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8288349979123488</v>
+        <v>-0.7828843139626613</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.948654699277377</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.959678768626838</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.990994681901059</v>
+        <v>-9.87611797202684</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8648409582591383</v>
+        <v>-0.8188902743094508</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.046273976698774</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.904148952795768</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.1385207699067</v>
+        <v>-10.02364406003248</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9209578371398233</v>
+        <v>-0.8750071531901358</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.193800064704418</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.818526856313954</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.34277894523657</v>
+        <v>-10.22790223536235</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9971479101531262</v>
+        <v>-0.9511972262034387</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.321439009318407</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.747456686664203</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.48458871944335</v>
+        <v>-10.36971200956913</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.049389265351406</v>
+        <v>-1.003438581401718</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.492717806963982</v>
+        <v>-2.469437978585626</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.649171962561294</v>
+        <v>1.663139859588308</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.4111188877759</v>
+        <v>-10.29624217790169</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.004629631191005</v>
+        <v>-0.9586789472413173</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.419247975296534</v>
+        <v>-2.395968146918177</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.708625563055184</v>
+        <v>1.722593460082198</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.58624330516245</v>
+        <v>-10.47136659528823</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.060124177398105</v>
+        <v>-1.014173493448418</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.594372392683078</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.618106133370775</v>
+        <v>1.632074030397789</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.82069539917694</v>
+        <v>-10.70581868930272</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.161124179905497</v>
+        <v>-1.11517349595581</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.594372392683078</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.610886968469179</v>
+        <v>1.624854865496193</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.10849924371418</v>
+        <v>-10.99362253383996</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.282917908494369</v>
+        <v>-1.236967224544682</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.882176237220316</v>
+        <v>-2.858896408841959</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.43153247097286</v>
+        <v>1.445500367999874</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.1612853993145</v>
+        <v>-11.04640868944028</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.302916580895944</v>
+        <v>-1.256965896946256</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.977851723802713</v>
+        <v>-2.954571895424356</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.375242968861978</v>
+        <v>1.389210865888992</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.28732219268279</v>
+        <v>-11.17244548280857</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.350637569614145</v>
+        <v>-1.304686885664457</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.95260010099297</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.393087671176938</v>
+        <v>1.407055568203952</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.23530667871398</v>
+        <v>-11.12042996883976</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.325841028340219</v>
+        <v>-1.279890344390531</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.95260010099297</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.397078006863339</v>
+        <v>1.411045903890353</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.3769785204381</v>
+        <v>-11.26210181056388</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.383984991928608</v>
+        <v>-1.338034307978921</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.95260010099297</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.395602779964597</v>
+        <v>1.409570676991611</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.32738767601326</v>
+        <v>-11.21251096613905</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.349095243993802</v>
+        <v>-1.303144560044114</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.903009256568136</v>
+        <v>-2.87972942818978</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.44041069678437</v>
+        <v>1.454378593811384</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.31458028300849</v>
+        <v>-11.19970357313427</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.357023420438576</v>
+        <v>-1.311072736488888</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.951865031577037</v>
+        <v>-2.928585203198681</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.398046098132346</v>
+        <v>1.41201399515936</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.08873513028908</v>
+        <v>-10.97385842041486</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.257106286314603</v>
+        <v>-1.211155602364915</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.909938355989873</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.432781176520853</v>
+        <v>1.446749073547867</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.96415647395149</v>
+        <v>-10.84927976407727</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.206135679223507</v>
+        <v>-1.160184995273819</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.909938355989873</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.433920321076912</v>
+        <v>1.447888218103926</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.01705176199578</v>
+        <v>-10.90217505212155</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.224660020279114</v>
+        <v>-1.178709336329426</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.904983009901427</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.439527302892087</v>
+        <v>1.453495199919101</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.94491858670789</v>
+        <v>-10.83004187683367</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.190073045925325</v>
+        <v>-1.144122361975637</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.904983009901427</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.445261007130724</v>
+        <v>1.459228904157738</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.87355219409825</v>
+        <v>-10.75867548422403</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.171263751275331</v>
+        <v>-1.125313067325643</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.833616617291779</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.478343580302647</v>
+        <v>1.492311477329662</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.60971532689418</v>
+        <v>-10.49483861701996</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.075612485706611</v>
+        <v>-1.029661801756923</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.833616617291779</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.46846009898974</v>
+        <v>1.482427996016754</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.34247352602578</v>
+        <v>-10.22759681615156</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9705503258586261</v>
+        <v>-0.9245996419089377</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.833616617291779</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.466625538490366</v>
+        <v>1.48059343551738</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.24456648734929</v>
+        <v>-10.12968977747507</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.93168782536149</v>
+        <v>-0.8857371414118025</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.765630867431223</v>
+        <v>-2.742351039052866</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.507116673433239</v>
+        <v>1.521084570460253</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.22061294637333</v>
+        <v>-10.10573623649911</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9214379028256139</v>
+        <v>-0.8754872188759255</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.741677326455265</v>
+        <v>-2.718397498076909</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.522157304164307</v>
+        <v>1.536125201191321</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.956553008050534</v>
+        <v>-9.841676298176314</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8290742436582468</v>
+        <v>-0.7831235597085588</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.477617388132469</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.667332950996233</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.249473384545697</v>
+        <v>-9.134596674671476</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5490294279166128</v>
+        <v>-0.5030787439669249</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.477617388132469</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.664545917335932</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.209289086179506</v>
+        <v>-9.094412376305286</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5326120846822953</v>
+        <v>-0.4866614007326073</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.437433089766278</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.689000120243488</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.129219290641702</v>
+        <v>-9.014342580767481</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5012173452464168</v>
+        <v>-0.4552666612967284</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.357363294228474</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.736408818786927</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291816</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.895738068412104</v>
+        <v>-8.780861358537884</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3999004275167253</v>
+        <v>-0.3539497435670369</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.123882071998876</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.884421980962539</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.74607167740459</v>
+        <v>-8.631194967530369</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3429260814266786</v>
+        <v>-0.2969753974769906</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.03097858075634</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.937271865395101</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.613796203773703</v>
+        <v>-8.498919493899482</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2946484052272966</v>
+        <v>-0.2486977212776087</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.898703107125453</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.01200463632066</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105958</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.423196529100549</v>
+        <v>-8.308319819226329</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2155934746703987</v>
+        <v>-0.1696427907207103</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.7081034324523</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.129179501812189</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.174196730416968</v>
+        <v>-8.059320020542748</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1030872139733074</v>
+        <v>-0.05713653002361907</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.7081034324523</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.142085843035847</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.279786720190073</v>
+        <v>-8.164910010315852</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2732991394817681</v>
+        <v>-0.2273484555320797</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.813693422225404</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.950755919572766</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987909</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.29852162230867</v>
+        <v>-8.183644912434449</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2322487584521205</v>
+        <v>-0.1862980745024321</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.819289431885536</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.995942655653773</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.15058158090107</v>
+        <v>-8.03570487102685</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2929516645772483</v>
+        <v>-0.2470009806275599</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.798968515976978</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.888256282510741</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409212</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.133423430769776</v>
+        <v>-8.018546720895555</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2948023907782087</v>
+        <v>-0.2488517068285203</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.781810365845684</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.889837186336039</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098116</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.089875023999085</v>
+        <v>-7.974998314124865</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2843436401650252</v>
+        <v>-0.2383929562153373</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.781810365845684</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.882876574240946</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.847726630545226</v>
+        <v>-7.732849920671007</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1730219284023389</v>
+        <v>-0.1270712444526509</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.781810365845684</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.897338928622089</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722823</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.739467493422705</v>
+        <v>-7.624590783548485</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1351861530941352</v>
+        <v>-0.08923546914444724</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.781810365845684</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.891871049081284</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792053</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.616176358605574</v>
+        <v>-7.501299648731354</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.08837160515670606</v>
+        <v>-0.04242092120701813</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.658519231028553</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.963343823982139</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919914</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.595027159702131</v>
+        <v>-7.480150449827911</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.07221094735800371</v>
+        <v>-0.02626026340831578</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.63737003212511</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.98373432156153</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318099</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.351261717718686</v>
+        <v>-7.236385007844467</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.02107593778242478</v>
+        <v>0.06702662173211271</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.63737003212511</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.979515029908581</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057532</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.249498897441391</v>
+        <v>-7.134622187567172</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.06390537981335864</v>
+        <v>0.1098560637630466</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.624150963732681</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.989570784864054</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279192</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.999648503492317</v>
+        <v>-6.884771793618097</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1565876123766907</v>
+        <v>0.2025382963263787</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.624150963732681</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.982312859847756</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011505</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.823756411024885</v>
+        <v>-6.708879701150664</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2305435728843124</v>
+        <v>0.2764942568340008</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.624150963732681</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.985911983368405</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392994</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.652309948002421</v>
+        <v>-6.537433238128201</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3124496641478514</v>
+        <v>0.3584003480975397</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.452704500710218</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.102107367236437</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632789</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.427276948333598</v>
+        <v>-6.312400238459378</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4014833416316774</v>
+        <v>0.4474340255813658</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.227671501041395</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.236147644654028</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883076</v>
+        <v>3.76461787988308</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.363641206099664</v>
+        <v>-6.248764496225443</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4316324395795688</v>
+        <v>0.4775831235292567</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.164035758807461</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.279023891048706</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.270641164893766</v>
+        <v>-6.155764455019545</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4500267148457238</v>
+        <v>0.4959773987954117</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.164035758807461</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.260218149832501</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242299</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.030210668088905</v>
+        <v>-5.915333958214685</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5479419901925451</v>
+        <v>0.5938926741422335</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9236052620026003</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.406219524540295</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367689</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.957968099917711</v>
+        <v>-5.84309139004349</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5807683312958432</v>
+        <v>0.6267190152455315</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9236052620026003</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.410148838375115</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879968</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.904969777636323</v>
+        <v>-5.790093067762102</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6026462441257383</v>
+        <v>0.6485969280754267</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8682690030006615</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.444029177693618</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502342</v>
+        <v>3.848616626502345</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.796164892156596</v>
+        <v>-5.681288182282375</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6431662695376228</v>
+        <v>0.6891169534873107</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8682690030006615</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.441027248913612</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.818668951675944</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.576144094119585</v>
+        <v>-5.461267384245365</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7327536257630411</v>
+        <v>0.7787043097127291</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7270491579326812</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.527338192965014</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.443276405056308</v>
+        <v>-5.328399695182087</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8017948841901754</v>
+        <v>0.8477455681398638</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7270491579326812</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.543232375766837</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496268</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.283761301536938</v>
+        <v>-5.168884591662717</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8667467700382252</v>
+        <v>0.9126974539879136</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5675340544133113</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.640087282318761</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577005</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.1390891564372</v>
+        <v>-5.02421244656298</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9347037306395602</v>
+        <v>0.9806544145892482</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4228619093135739</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.736978671940043</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.73583922294211</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.198963983794893</v>
+        <v>-5.084087273920672</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.8967912910979088</v>
+        <v>0.9427419750475972</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.482736736671266</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.687091266926854</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674522</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.112164486015883</v>
+        <v>-4.997287776141663</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9539115835320788</v>
+        <v>0.999862267481767</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.482736736671266</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.70949176024942</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430701</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.114634192477689</v>
+        <v>-4.999757482603469</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9529961023207685</v>
+        <v>0.9989467862704566</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4852064431330722</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.708082337745748</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003609</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.1830043788017</v>
+        <v>-5.068127668927479</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9366549502658663</v>
+        <v>0.9826056342155547</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4759307440968572</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.72465467964218</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508377</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.291542559717834</v>
+        <v>-5.176665849843613</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8836763865313042</v>
+        <v>0.9296270704809921</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4759307440968572</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.715091388274071</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.71090673141771</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.149557317538017</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.314362255229757</v>
+        <v>-5.199566622745779</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.023455991132367</v>
+        <v>0.7451763263605127</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4759307440968572</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.863998871079903</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205906</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.154124549529805</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.138887995437289</v>
+        <v>-5.02409236295331</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.098212927041142</v>
+        <v>0.8199332622692883</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4759307440968572</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.868566103071691</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225451</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.129866578291012</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.249824248078538</v>
+        <v>-5.135028615594559</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.02958045474585</v>
+        <v>0.7513007899739956</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4759307440968572</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.844308131832898</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111302</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.132997963510918</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.452850825621771</v>
+        <v>-5.338055193137792</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.951501208948462</v>
+        <v>0.6732215441766081</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6789573216400906</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.725623570526864</v>
+        <v>2.415393549788432</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.14317034994305</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.294925226686478</v>
+        <v>-5.180129594202499</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.024843834954712</v>
+        <v>0.7465641701828578</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6789573216400906</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.735795956958996</v>
+        <v>2.425565936220564</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742307</v>
       </c>
       <c r="C1943" t="n">
-        <v>3.13811662051691</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.2086817636601</v>
+        <v>-5.093886131176121</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.054287490739123</v>
+        <v>0.7760078259672691</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6789573216400906</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.730742227532856</v>
+        <v>2.420512206794424</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316054</v>
       </c>
       <c r="C1944" t="n">
-        <v>3.129892395961436</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.25398858305908</v>
+        <v>-5.139192950575101</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.027940538424057</v>
+        <v>0.7496608736522026</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7197674846493214</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.698031905171844</v>
+        <v>2.387801884433411</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803199</v>
       </c>
       <c r="C1945" t="n">
-        <v>3.130444268994538</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.283021687761381</v>
+        <v>-5.168226055277402</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.016879169576238</v>
+        <v>0.7385995048043839</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7197674846493214</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.698583778204945</v>
+        <v>2.388353757466513</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809505</v>
       </c>
       <c r="C1946" t="n">
-        <v>3.059716960885903</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.190211206310521</v>
+        <v>-5.075415573826542</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9832760540479475</v>
+        <v>0.7049963892760931</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.626957003198462</v>
+        <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.683542758966826</v>
+        <v>2.373312738228394</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560433</v>
       </c>
       <c r="C1947" t="n">
-        <v>3.061590436810504</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.234600675639949</v>
+        <v>-5.11980504315597</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9673937422407772</v>
+        <v>0.6891140774689233</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6713464725278897</v>
+        <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.65878255329377</v>
+        <v>2.348552532555338</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472745</v>
       </c>
       <c r="C1948" t="n">
-        <v>3.056666145322227</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.121929457403699</v>
+        <v>-5.00713382491972</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.007537938047</v>
+        <v>0.7292582732751463</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5586752542916396</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.721460992747244</v>
+        <v>2.411230972008811</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798544</v>
       </c>
       <c r="C1949" t="n">
-        <v>3.062157441152894</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-5.009552456221026</v>
+        <v>-4.894756823737047</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.057980034350737</v>
+        <v>0.7797003695788827</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5586752542916396</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.726952288577911</v>
+        <v>2.416722267839479</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498872</v>
       </c>
       <c r="C1950" t="n">
-        <v>3.073654642921433</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.207787025107756</v>
+        <v>-5.092991392623778</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9901834085645835</v>
+        <v>0.7119037437927291</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7569098231783702</v>
+        <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.619508749014412</v>
+        <v>2.309278728275979</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705332</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.912010362922087</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.290788306133035</v>
+        <v>-5.175992673649056</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7953386161551252</v>
+        <v>0.5170589513832708</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7754807077055439</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.446721938298761</v>
+        <v>2.136491917560329</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729277</v>
       </c>
       <c r="C1952" t="n">
-        <v>3.032160023641292</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.399402384576367</v>
+        <v>-5.284606752092388</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8720426454969985</v>
+        <v>0.5937629807251441</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7754807077055439</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.566871599017966</v>
+        <v>2.256641578279534</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190776</v>
       </c>
       <c r="C1953" t="n">
-        <v>3.046673049743615</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.486000967557469</v>
+        <v>-5.371205335073491</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8519162384068801</v>
+        <v>0.5736365736350262</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7754807077055439</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.581384625120289</v>
+        <v>2.271154604381857</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913432</v>
       </c>
       <c r="C1954" t="n">
-        <v>3.044092491085984</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.533669797223982</v>
+        <v>-5.332821672515339</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8302681478826441</v>
+        <v>0.586409480000655</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.8231495373720561</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.55020276866275</v>
+        <v>2.291604243259116</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532492</v>
       </c>
       <c r="C1955" t="n">
-        <v>3.040821519931286</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.356553467188816</v>
+        <v>-5.155705342480173</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8978437087420121</v>
+        <v>0.6539850408600234</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.8231495373720561</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.546931797508052</v>
+        <v>2.288333272104418</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793909</v>
       </c>
       <c r="C1956" t="n">
-        <v>3.041504911693199</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.326851343212522</v>
+        <v>-5.12600321850388</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9104079500944429</v>
+        <v>0.6665492822124541</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.8276196625873695</v>
+        <v>-0.7182873419843501</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.544933114140778</v>
+        <v>2.286334588737144</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011242</v>
       </c>
       <c r="C1957" t="n">
-        <v>3.035291886999613</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.147475921973754</v>
+        <v>-4.946627797265112</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9759450938963643</v>
+        <v>0.7320864260143756</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6708429044166508</v>
+        <v>-0.5615105838136314</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.632786144349623</v>
+        <v>2.374187618945989</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982235</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
-        <v>3.016099342331203</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.19249013549436</v>
+        <v>-4.991642010785718</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9387468638197118</v>
+        <v>0.6948881959377229</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.7011917997312554</v>
+        <v>-0.591859479128236</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.59538426249245</v>
+        <v>2.336785737088816</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509544</v>
       </c>
       <c r="C1959" t="n">
-        <v>3.021790904670149</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.459494645766795</v>
+        <v>-5.258646521058153</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8376366220496836</v>
+        <v>0.5937779541676949</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.895554837774204</v>
+        <v>-0.7862225171711845</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.484458002005627</v>
+        <v>2.225859476601993</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760819</v>
       </c>
       <c r="C1960" t="n">
-        <v>3.02099482656665</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.560692427203968</v>
+        <v>-5.359844302495326</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7963614313713157</v>
+        <v>0.5525027634893269</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9639636513195231</v>
+        <v>-0.8546313307165037</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.442616635774937</v>
+        <v>2.184018110371303</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815465</v>
       </c>
       <c r="C1961" t="n">
-        <v>3.018594788120967</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.528216841033196</v>
+        <v>-5.327368716324553</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8069516273939414</v>
+        <v>0.5630929595119527</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9639636513195231</v>
+        <v>-0.8546313307165037</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.440216597329253</v>
+        <v>2.18161807192562</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378109</v>
       </c>
       <c r="C1962" t="n">
-        <v>3.015119507329212</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.509178713325898</v>
+        <v>-5.308330588617256</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8110915976851052</v>
+        <v>0.5672329298031165</v>
       </c>
       <c r="F1962" t="n">
-        <v>-1.022147262650718</v>
+        <v>-0.9128149420476982</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.401831149738782</v>
+        <v>2.143232624335147</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.192701376267892</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.540305344476517</v>
+        <v>-5.339457219767874</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9762228141635383</v>
+        <v>0.7323641462815496</v>
       </c>
       <c r="F1963" t="n">
-        <v>-1.022147262650718</v>
+        <v>-0.9128149420476982</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.579413018677462</v>
+        <v>2.320814493273828</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067875</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.193534705254026</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.592625725077308</v>
+        <v>-5.391777600368666</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9561279909093554</v>
+        <v>0.7122693230273667</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9872004026418454</v>
+        <v>-0.877868082038826</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.601214463668919</v>
+        <v>2.342615938265285</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789132</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.199543235650952</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.612883023606266</v>
+        <v>-5.412034898897624</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.954033601894698</v>
+        <v>0.7101749340127093</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9872004026418454</v>
+        <v>-0.877868082038826</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.607222994065845</v>
+        <v>2.348624468662211</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519916</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.278695883442974</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.465140053371264</v>
+        <v>-5.264291928662622</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.092283437780721</v>
+        <v>0.8484247698987324</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.8193930454069622</v>
+        <v>-0.7100607248039429</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.787060056198797</v>
+        <v>2.528461530795163</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181178</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.281489504974455</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.567154735902485</v>
+        <v>-5.366306611193843</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.054271186299713</v>
+        <v>0.8104125184177247</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.8193930454069622</v>
+        <v>-0.7100607248039429</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.789853677730278</v>
+        <v>2.531255152326644</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394738</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.282151853366113</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.430545391808392</v>
+        <v>-5.22969726709975</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.109577272329009</v>
+        <v>0.8657186044470202</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6827837013128697</v>
+        <v>-0.5734513807098505</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.872481632578392</v>
+        <v>2.613883107174757</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489062</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.281232330106223</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.573310724631042</v>
+        <v>-5.3724625999224</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.051551615940059</v>
+        <v>0.8076929480580701</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.8255490341355201</v>
+        <v>-0.7162167135325008</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.785902909624911</v>
+        <v>2.527304384221277</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.347567883903044</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.51101272585492</v>
+        <v>-5.310164601146278</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.142806369247329</v>
+        <v>0.8989477013653402</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.8255490341355201</v>
+        <v>-0.7162167135325008</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.852238463421732</v>
+        <v>2.593639938018098</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992198</v>
       </c>
       <c r="C1971" t="n">
-        <v>3.056148756292442</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.309222528189762</v>
+        <v>-5.10837440348112</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9321033207027902</v>
+        <v>0.6882446528208015</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.6275308419663657</v>
+        <v>-0.5181985213633464</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.679630251112623</v>
+        <v>2.421031725708989</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852431</v>
       </c>
       <c r="C1972" t="n">
-        <v>3.126438988614618</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.249331846547169</v>
+        <v>-5.048483721838527</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.026349825682003</v>
+        <v>0.7824911578000138</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5676401603237722</v>
+        <v>-0.458307839720753</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.785854892420355</v>
+        <v>2.527256367016721</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319554</v>
       </c>
       <c r="C1973" t="n">
-        <v>3.141066724730661</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.347072391172143</v>
+        <v>-5.146224266463501</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.001881343948057</v>
+        <v>0.7580226760660675</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5835294384567524</v>
+        <v>-0.4741971178537331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.79094906165661</v>
+        <v>2.532350536252976</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489392</v>
       </c>
       <c r="C1974" t="n">
-        <v>3.139602705555333</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.523410151295073</v>
+        <v>-5.32256202658643</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9298822207235564</v>
+        <v>0.6860235528415677</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7598671985796819</v>
+        <v>-0.6505348779766625</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.683682386407524</v>
+        <v>2.42508386100389</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397801</v>
       </c>
       <c r="C1975" t="n">
-        <v>3.138094323595261</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.52272077913385</v>
+        <v>-5.321872654425207</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9286495876279743</v>
+        <v>0.6847909197459856</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7598671985796819</v>
+        <v>-0.6505348779766625</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.682174004447452</v>
+        <v>2.423575479043818</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.83602339102497</v>
       </c>
       <c r="C1976" t="n">
-        <v>3.137957191030698</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.529291744188442</v>
+        <v>-5.3284436194798</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9258840690415733</v>
+        <v>0.6820254011595845</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7664381636342747</v>
+        <v>-0.6571058430312555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.678094292850133</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863233</v>
       </c>
       <c r="C1977" t="n">
-        <v>3.137957191030698</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.52133777389367</v>
+        <v>-5.320489649185028</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9290656571594824</v>
+        <v>0.6852069892774937</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7664381636342747</v>
+        <v>-0.6571058430312555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.678094292850133</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947592</v>
       </c>
       <c r="C1978" t="n">
-        <v>3.144338948058502</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.510964397560583</v>
+        <v>-5.310116272851941</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9395967647205219</v>
+        <v>0.6957380968385327</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7560647873011874</v>
+        <v>-0.6467324666981682</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.69070007567779</v>
+        <v>2.432101550274156</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326884</v>
       </c>
       <c r="C1979" t="n">
-        <v>3.149231321433227</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.383280087766287</v>
+        <v>-5.182431963057645</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9955628620129651</v>
+        <v>0.7517041941309763</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.628380477506891</v>
+        <v>-0.5190481569038717</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.772203034929093</v>
+        <v>2.513604509525459</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.82883791131456</v>
       </c>
       <c r="C1980" t="n">
-        <v>3.135985993909099</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.443946678168675</v>
+        <v>-5.243098553460033</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9580508983278819</v>
+        <v>0.7141922304458932</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.7100787942254246</v>
+        <v>-0.6007464736224054</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.709938717373845</v>
+        <v>2.451340191970211</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690035</v>
       </c>
       <c r="C1981" t="n">
-        <v>3.140083696519728</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.37895281823503</v>
+        <v>-5.178104693526388</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9881461449119686</v>
+        <v>0.7442874770299799</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6832481796212693</v>
+        <v>-0.57391585901825</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.730134788746966</v>
+        <v>2.471536263343332</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674318</v>
       </c>
       <c r="C1982" t="n">
-        <v>3.144244636150806</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.479711453992028</v>
+        <v>-5.278863329283386</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9520036302402475</v>
+        <v>0.7081449623582587</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7720737483482747</v>
+        <v>-0.6627414277452555</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.681000387141841</v>
+        <v>2.422401861738207</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163227</v>
       </c>
       <c r="C1983" t="n">
-        <v>3.150124238678643</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.435508616906128</v>
+        <v>-5.234660492197485</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9755643676024448</v>
+        <v>0.7317056997204561</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.7278709112623742</v>
+        <v>-0.618538590659355</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.713401691921219</v>
+        <v>2.454803166517585</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022912</v>
       </c>
       <c r="C1984" t="n">
-        <v>3.148534239147891</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.47248764456957</v>
+        <v>-5.271639519860928</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9591827570063152</v>
+        <v>0.7153240891243264</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6908970094710437</v>
+        <v>-0.5815646888680245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.733996033465265</v>
+        <v>2.475397508061631</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042146</v>
       </c>
       <c r="C1985" t="n">
-        <v>3.19978200433093</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.492545723434411</v>
+        <v>-5.291697598725769</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.002407290643418</v>
+        <v>0.7585486227614298</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6908970094710437</v>
+        <v>-0.5815646888680245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.785243798648304</v>
+        <v>2.52664527324467</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865367715078289</v>
       </c>
       <c r="C1986" t="n">
-        <v>3.198222708925183</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.37084192364795</v>
+        <v>-5.251766925547878</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.049529515152256</v>
+        <v>0.7729615966268391</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5691932096845825</v>
+        <v>-0.5416340156901341</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.856706783114434</v>
+        <v>2.549044381745658</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.762257370250698</v>
+        <v>3.762257370250703</v>
       </c>
       <c r="C1987" t="n">
-        <v>3.182797099657121</v>
+        <v>2.858599181891675</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.37084192364795</v>
+        <v>-5.251766925547878</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.049529515152256</v>
+        <v>0.7729615966268391</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.5691932096845825</v>
+        <v>-0.5416340156901341</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.175860896643488</v>
+        <v>2.851662978878043</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240606.xlsx
+++ b/tame_output/ON/bt/strategyON_20240606.xlsx
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764399</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955331</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232415</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436231</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017774</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839729</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388732</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626478</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291816</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105958</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987909</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409212</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098116</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722823</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792053</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919914</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318099</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057532</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279192</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011505</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392994</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632789</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242299</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367689</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879968</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.848616626502342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675944</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496268</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577005</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.73583922294211</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674522</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430701</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003609</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508377</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.71090673141771</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111302</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742307</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316054</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803199</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809505</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472745</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798544</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498872</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705332</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729277</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190776</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913432</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532492</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793909</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011242</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982237</v>
+        <v>3.716991718982235</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509544</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760819</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815465</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378109</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789132</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519916</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181178</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394738</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489062</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992198</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319554</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489392</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397801</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102497</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863233</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947592</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326884</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82883791131456</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690035</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674318</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163227</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022912</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042146</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078289</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.762257370250703</v>
+        <v>3.762257370250698</v>
       </c>
       <c r="C1987" t="n">
         <v>2.858599181891675</v>

--- a/tame_output/ON/bt/strategyON_20240606.xlsx
+++ b/tame_output/ON/bt/strategyON_20240606.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-52.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.0%</t>
+          <t>449.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.7%</t>
+          <t>-687.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-298.9%</t>
+          <t>-300.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-278.2%</t>
+          <t>-256.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-160.9%</t>
+          <t>-179.7%</t>
         </is>
       </c>
     </row>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.49483861701996</v>
+        <v>-10.72203323026563</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.029661801756923</v>
+        <v>-1.120539647055193</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.22759681615156</v>
+        <v>-10.45479142939723</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9245996419089377</v>
+        <v>-1.015477487207208</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.12968977747507</v>
+        <v>-10.35688439072074</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8857371414118025</v>
+        <v>-0.976614986710072</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.10573623649911</v>
+        <v>-10.33293084974479</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8754872188759255</v>
+        <v>-0.9663650641741959</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.841676298176314</v>
+        <v>-10.06887091142199</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7831235597085588</v>
+        <v>-0.8740014050068288</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.134596674671476</v>
+        <v>-9.361791287917152</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5030787439669249</v>
+        <v>-0.5939565892651948</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.094412376305286</v>
+        <v>-9.321606989550961</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4866614007326073</v>
+        <v>-0.5775392460308773</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.014342580767481</v>
+        <v>-9.241537194013157</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4552666612967284</v>
+        <v>-0.5461445065949988</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.780861358537884</v>
+        <v>-9.008055971783559</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3539497435670369</v>
+        <v>-0.4448275888653073</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.631194967530369</v>
+        <v>-8.858389580776045</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2969753974769906</v>
+        <v>-0.3878532427752606</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.498919493899482</v>
+        <v>-8.726114107145158</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2486977212776087</v>
+        <v>-0.3395755665758786</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.308319819226329</v>
+        <v>-8.535514432472004</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1696427907207103</v>
+        <v>-0.2605206360189807</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.059320020542748</v>
+        <v>-8.286514633788423</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.05713653002361907</v>
+        <v>-0.1480143753218894</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.164910010315852</v>
+        <v>-8.392104623561528</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2273484555320797</v>
+        <v>-0.3182263008303501</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.183644912434449</v>
+        <v>-8.410839525680124</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1862980745024321</v>
+        <v>-0.2771759198007024</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.03570487102685</v>
+        <v>-8.262899484272525</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2470009806275599</v>
+        <v>-0.3378788259258303</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.018546720895555</v>
+        <v>-8.245741334141231</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2488517068285203</v>
+        <v>-0.3397295521267907</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.974998314124865</v>
+        <v>-8.20219292737054</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2383929562153373</v>
+        <v>-0.3292708015136072</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.732849920671007</v>
+        <v>-7.960044533916681</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1270712444526509</v>
+        <v>-0.2179490897509209</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.624590783548485</v>
+        <v>-7.85178539679416</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.08923546914444724</v>
+        <v>-0.1801133144427172</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.501299648731354</v>
+        <v>-7.728494261977029</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.04242092120701813</v>
+        <v>-0.133298766505288</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.480150449827911</v>
+        <v>-7.707345063073586</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02626026340831578</v>
+        <v>-0.1171381087065857</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.236385007844467</v>
+        <v>-7.463579621090141</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.06702662173211271</v>
+        <v>-0.02385122356615721</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.134622187567172</v>
+        <v>-7.361816800812846</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1098560637630466</v>
+        <v>0.01897821846477665</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.884771793618097</v>
+        <v>-7.111966406863772</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2025382963263787</v>
+        <v>0.1116604510281087</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.708879701150664</v>
+        <v>-6.93607431439634</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2764942568340008</v>
+        <v>0.1856164115357304</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.537433238128201</v>
+        <v>-6.764627851373876</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3584003480975397</v>
+        <v>0.2675225027992694</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.312400238459378</v>
+        <v>-6.539594851705053</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4474340255813658</v>
+        <v>0.3565561802830954</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.248764496225443</v>
+        <v>-6.475959109471119</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4775831235292567</v>
+        <v>0.3867052782309868</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.155764455019545</v>
+        <v>-6.382959068265221</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4959773987954117</v>
+        <v>0.4050995534971418</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.915333958214685</v>
+        <v>-6.14252857146036</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5938926741422335</v>
+        <v>0.5030148288439631</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.84309139004349</v>
+        <v>-6.070286003289166</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6267190152455315</v>
+        <v>0.5358411699472612</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.790093067762102</v>
+        <v>-6.017287681007778</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6485969280754267</v>
+        <v>0.5577190827771563</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.681288182282375</v>
+        <v>-5.908482795528051</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6891169534873107</v>
+        <v>0.5982391081890408</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.461267384245365</v>
+        <v>-5.68846199749104</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7787043097127291</v>
+        <v>0.6878264644144592</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.328399695182087</v>
+        <v>-5.555594308427763</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8477455681398638</v>
+        <v>0.7568677228415934</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.168884591662717</v>
+        <v>-5.396079204908393</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9126974539879136</v>
+        <v>0.8218196086896432</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.02421244656298</v>
+        <v>-5.251407059808655</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9806544145892482</v>
+        <v>0.8897765692909783</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.084087273920672</v>
+        <v>-5.311281887166348</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9427419750475972</v>
+        <v>0.8518641297493268</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.997287776141663</v>
+        <v>-5.224482389387338</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.999862267481767</v>
+        <v>0.9089844221834968</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.999757482603469</v>
+        <v>-5.226952095849144</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9989467862704566</v>
+        <v>0.9080689409721865</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.068127668927479</v>
+        <v>-5.295322282173155</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9826056342155547</v>
+        <v>0.8917277889172843</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.176665849843613</v>
+        <v>-5.403860463089289</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9296270704809921</v>
+        <v>0.8387492251827222</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.199566622745779</v>
+        <v>-5.426761235991455</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7451763263605127</v>
+        <v>0.6542984810622423</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.02409236295331</v>
+        <v>-5.251286976198985</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8199332622692883</v>
+        <v>0.7290554169710179</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.135028615594559</v>
+        <v>-5.362223228840234</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7513007899739956</v>
+        <v>0.6604229446757257</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.338055193137792</v>
+        <v>-5.565249806383467</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6732215441766081</v>
+        <v>0.5823436988783377</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.180129594202499</v>
+        <v>-5.407324207448174</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7465641701828578</v>
+        <v>0.6556863248845874</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.093886131176121</v>
+        <v>-5.321080744421796</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7760078259672691</v>
+        <v>0.6851299806689988</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.139192950575101</v>
+        <v>-5.366387563820776</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7496608736522026</v>
+        <v>0.6587830283539327</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.168226055277402</v>
+        <v>-5.395420668523077</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7385995048043839</v>
+        <v>0.6477216595061135</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.075415573826542</v>
+        <v>-5.302610187072218</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7049963892760931</v>
+        <v>0.6141185439778232</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.11980504315597</v>
+        <v>-5.346999656401645</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6891140774689233</v>
+        <v>0.5982362321706529</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.00713382491972</v>
+        <v>-5.234328438165395</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7292582732751463</v>
+        <v>0.6383804279768759</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.894756823737047</v>
+        <v>-5.121951436982722</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7797003695788827</v>
+        <v>0.6888225242806123</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.092991392623778</v>
+        <v>-5.320186005869453</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7119037437927291</v>
+        <v>0.6210258984944592</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.175992673649056</v>
+        <v>-5.403187286894732</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5170589513832708</v>
+        <v>0.4261811060850009</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.284606752092388</v>
+        <v>-5.511801365338063</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5937629807251441</v>
+        <v>0.5028851354268742</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.371205335073491</v>
+        <v>-5.598399948319166</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5736365736350262</v>
+        <v>0.4827587283367558</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.332821672515339</v>
+        <v>-5.560016285761015</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.586409480000655</v>
+        <v>0.495531634702385</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.155705342480173</v>
+        <v>-5.382899955725849</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6539850408600234</v>
+        <v>0.5631071955617535</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.12600321850388</v>
+        <v>-5.353197831749555</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6665492822124541</v>
+        <v>0.5756714369141838</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7182873419843501</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.946627797265112</v>
+        <v>-5.173822410510788</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7320864260143756</v>
+        <v>0.6412085807161052</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.5615105838136314</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.991642010785718</v>
+        <v>-5.218836624031393</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6948881959377229</v>
+        <v>0.6040103506394527</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.591859479128236</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.258646521058153</v>
+        <v>-5.485841134303828</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5937779541676949</v>
+        <v>0.5029001088694245</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.7862225171711845</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.359844302495326</v>
+        <v>-5.587038915741001</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5525027634893269</v>
+        <v>0.461624918191057</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.8546313307165037</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.327368716324553</v>
+        <v>-5.554563329570229</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5630929595119527</v>
+        <v>0.4722151142136823</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.8546313307165037</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.308330588617256</v>
+        <v>-5.535525201862932</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5672329298031165</v>
+        <v>0.4763550845048461</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9128149420476982</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.339457219767874</v>
+        <v>-5.56665183301355</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7323641462815496</v>
+        <v>0.6414863009832796</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9128149420476982</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.391777600368666</v>
+        <v>-5.618972213614342</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7122693230273667</v>
+        <v>0.6213914777290963</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.877868082038826</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.412034898897624</v>
+        <v>-5.6392295121433</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7101749340127093</v>
+        <v>0.6192970887144389</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.877868082038826</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.264291928662622</v>
+        <v>-5.491486541908297</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8484247698987324</v>
+        <v>0.757546924600462</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7100607248039429</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.366306611193843</v>
+        <v>-5.593501224439518</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8104125184177247</v>
+        <v>0.7195346731194543</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7100607248039429</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.22969726709975</v>
+        <v>-5.456891880345426</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8657186044470202</v>
+        <v>0.7748407591487498</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.5734513807098505</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.3724625999224</v>
+        <v>-5.599657213168076</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8076929480580701</v>
+        <v>0.7168151027598002</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7162167135325008</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.310164601146278</v>
+        <v>-5.537359214391953</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8989477013653402</v>
+        <v>0.8080698560670698</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7162167135325008</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.10837440348112</v>
+        <v>-5.335569016726796</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6882446528208015</v>
+        <v>0.5973668075225311</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.5181985213633464</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.048483721838527</v>
+        <v>-5.275678335084202</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7824911578000138</v>
+        <v>0.6916133125017438</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.458307839720753</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.146224266463501</v>
+        <v>-5.373418879709177</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7580226760660675</v>
+        <v>0.6671448307677976</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.4741971178537331</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.32256202658643</v>
+        <v>-5.549756639832106</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6860235528415677</v>
+        <v>0.5951457075432973</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.6505348779766625</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.321872654425207</v>
+        <v>-5.549067267670883</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6847909197459856</v>
+        <v>0.5939130744477152</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.6505348779766625</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.3284436194798</v>
+        <v>-5.555638232725475</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6820254011595845</v>
+        <v>0.5911475558613146</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.6571058430312555</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.320489649185028</v>
+        <v>-5.547684262430703</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6852069892774937</v>
+        <v>0.5943291439792233</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.6571058430312555</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.310116272851941</v>
+        <v>-5.537310886097616</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6957380968385327</v>
+        <v>0.6048602515402628</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.6467324666981682</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.182431963057645</v>
+        <v>-5.40962657630332</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7517041941309763</v>
+        <v>0.660826348832706</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5190481569038717</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.243098553460033</v>
+        <v>-5.470293166705709</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7141922304458932</v>
+        <v>0.6233143851476228</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.6007464736224054</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.178104693526388</v>
+        <v>-5.405299306772063</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7442874770299799</v>
+        <v>0.6534096317317095</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.57391585901825</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.278863329283386</v>
+        <v>-5.506057942529061</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7081449623582587</v>
+        <v>0.6172671170599884</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.6627414277452555</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.234660492197485</v>
+        <v>-5.461855105443161</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7317056997204561</v>
+        <v>0.6408278544221857</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.618538590659355</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.271639519860928</v>
+        <v>-5.498834133106604</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7153240891243264</v>
+        <v>0.6244462438260561</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.5815646888680245</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.291697598725769</v>
+        <v>-5.518892211971444</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7585486227614298</v>
+        <v>0.6676707774631594</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.5815646888680245</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.251766925547878</v>
+        <v>-5.478961538793554</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7729615966268391</v>
+        <v>0.6820837513285687</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.5416340156901341</v>
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.762257370250698</v>
+        <v>3.464663985310515</v>
       </c>
       <c r="C1987" t="n">
         <v>2.858599181891675</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.251766925547878</v>
+        <v>-5.262668825881008</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7729615966268391</v>
+        <v>0.7531752272255248</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.5416340156901341</v>
+        <v>-0.3253413027775883</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.851662978878043</v>
+        <v>2.663394400225122</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240606.xlsx
+++ b/tame_output/ON/bt/strategyON_20240606.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-24.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.1%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.5%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-687.8%</t>
+          <t>-688.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-300.9%</t>
+          <t>-300.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-256.5%</t>
+          <t>-274.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-179.7%</t>
+          <t>-189.2%</t>
         </is>
       </c>
     </row>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.72203323026563</v>
+        <v>-10.49483861701996</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.120539647055193</v>
+        <v>-1.029661801756923</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.45479142939723</v>
+        <v>-10.22759681615156</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.015477487207208</v>
+        <v>-0.9245996419089377</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.35688439072074</v>
+        <v>-10.12968977747507</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.976614986710072</v>
+        <v>-0.8857371414118025</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.33293084974479</v>
+        <v>-10.10573623649911</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9663650641741959</v>
+        <v>-0.8754872188759255</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.06887091142199</v>
+        <v>-9.841676298176314</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8740014050068288</v>
+        <v>-0.7831235597085588</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.361791287917152</v>
+        <v>-9.134596674671476</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5939565892651948</v>
+        <v>-0.5030787439669249</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.321606989550961</v>
+        <v>-9.094412376305286</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5775392460308773</v>
+        <v>-0.4866614007326073</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.241537194013157</v>
+        <v>-9.014342580767481</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5461445065949988</v>
+        <v>-0.4552666612967284</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.008055971783559</v>
+        <v>-8.780861358537884</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4448275888653073</v>
+        <v>-0.3539497435670369</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.858389580776045</v>
+        <v>-8.631194967530369</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3878532427752606</v>
+        <v>-0.2969753974769906</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.726114107145158</v>
+        <v>-8.498919493899482</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3395755665758786</v>
+        <v>-0.2486977212776087</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.535514432472004</v>
+        <v>-8.308319819226329</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2605206360189807</v>
+        <v>-0.1696427907207103</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.286514633788423</v>
+        <v>-8.059320020542748</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1480143753218894</v>
+        <v>-0.05713653002361907</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.392104623561528</v>
+        <v>-8.164910010315852</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3182263008303501</v>
+        <v>-0.2273484555320797</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.410839525680124</v>
+        <v>-8.183644912434449</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2771759198007024</v>
+        <v>-0.1862980745024321</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.262899484272525</v>
+        <v>-8.03570487102685</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3378788259258303</v>
+        <v>-0.2470009806275599</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.245741334141231</v>
+        <v>-8.018546720895555</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3397295521267907</v>
+        <v>-0.2488517068285203</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.20219292737054</v>
+        <v>-7.974998314124865</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3292708015136072</v>
+        <v>-0.2383929562153373</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.960044533916681</v>
+        <v>-7.732849920671007</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2179490897509209</v>
+        <v>-0.1270712444526509</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.85178539679416</v>
+        <v>-7.624590783548485</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1801133144427172</v>
+        <v>-0.08923546914444724</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.728494261977029</v>
+        <v>-7.501299648731354</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.133298766505288</v>
+        <v>-0.04242092120701813</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.707345063073586</v>
+        <v>-7.480150449827911</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1171381087065857</v>
+        <v>-0.02626026340831578</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.463579621090141</v>
+        <v>-7.236385007844467</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.02385122356615721</v>
+        <v>0.06702662173211271</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.361816800812846</v>
+        <v>-7.134622187567172</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.01897821846477665</v>
+        <v>0.1098560637630466</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.111966406863772</v>
+        <v>-6.884771793618097</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1116604510281087</v>
+        <v>0.2025382963263787</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.93607431439634</v>
+        <v>-6.708879701150664</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1856164115357304</v>
+        <v>0.2764942568340008</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.764627851373876</v>
+        <v>-6.537433238128201</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2675225027992694</v>
+        <v>0.3584003480975397</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.539594851705053</v>
+        <v>-6.312400238459378</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3565561802830954</v>
+        <v>0.4474340255813658</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883076</v>
+        <v>3.764617879883077</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.475959109471119</v>
+        <v>-6.248764496225443</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3867052782309868</v>
+        <v>0.4775831235292567</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.382959068265221</v>
+        <v>-6.205002314919602</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4050995534971418</v>
+        <v>0.4762822548353891</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.14252857146036</v>
+        <v>-5.964571818114742</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5030148288439631</v>
+        <v>0.5741975301822109</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.070286003289166</v>
+        <v>-5.892329249943547</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5358411699472612</v>
+        <v>0.6070238712855089</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879968</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.017287681007778</v>
+        <v>-5.839330927662159</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5577190827771563</v>
+        <v>0.6289017841154041</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502342</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.908482795528051</v>
+        <v>-5.730526042182432</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.5982391081890408</v>
+        <v>0.6694218095272881</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.68846199749104</v>
+        <v>-5.510505244145421</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.6878264644144592</v>
+        <v>0.7590091657527065</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.555594308427763</v>
+        <v>-5.377637555082144</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.7568677228415934</v>
+        <v>0.8280504241798408</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.396079204908393</v>
+        <v>-5.218122451562774</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8218196086896432</v>
+        <v>0.8930023100278905</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.251407059808655</v>
+        <v>-5.073450306463037</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.8897765692909783</v>
+        <v>0.9609592706292256</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.311281887166348</v>
+        <v>-5.133325133820729</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.8518641297493268</v>
+        <v>0.9230468310875746</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.224482389387338</v>
+        <v>-5.04652563604172</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9089844221834968</v>
+        <v>0.9801671235217442</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.226952095849144</v>
+        <v>-5.048995342503526</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9080689409721865</v>
+        <v>0.9792516423104338</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.295322282173155</v>
+        <v>-5.117365528827536</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.8917277889172843</v>
+        <v>0.9629104902555321</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.403860463089289</v>
+        <v>-5.22590370974367</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8387492251827222</v>
+        <v>0.9099319265209695</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.426761235991455</v>
+        <v>-5.256896869072375</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.6542984810622423</v>
+        <v>0.7222442278298744</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205902</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.251286976198985</v>
+        <v>-5.081422609279906</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7290554169710179</v>
+        <v>0.7970011637386496</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.362223228840234</v>
+        <v>-5.192358861921155</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.6604229446757257</v>
+        <v>0.7283686914433569</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.565249806383467</v>
+        <v>-5.395385439464389</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.5823436988783377</v>
+        <v>0.6502894456459694</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264167</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.407324207448174</v>
+        <v>-5.237459840529096</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.6556863248845874</v>
+        <v>0.7236320716522191</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742303</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.321080744421796</v>
+        <v>-5.151216377502718</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.6851299806689988</v>
+        <v>0.7530757274366304</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.366387563820776</v>
+        <v>-5.196523196901698</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.6587830283539327</v>
+        <v>0.7267287751215639</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803195</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.395420668523077</v>
+        <v>-5.225556301603999</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.6477216595061135</v>
+        <v>0.7156674062737451</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.302610187072218</v>
+        <v>-5.132745820153139</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6141185439778232</v>
+        <v>0.6820642907454544</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.346999656401645</v>
+        <v>-5.177135289482567</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.5982362321706529</v>
+        <v>0.6661819789382846</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.234328438165395</v>
+        <v>-5.064464071246316</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6383804279768759</v>
+        <v>0.7063261747445075</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-5.121951436982722</v>
+        <v>-4.952087070063643</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.6888225242806123</v>
+        <v>0.756768271048244</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498868</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.320186005869453</v>
+        <v>-5.150321638950374</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6210258984944592</v>
+        <v>0.6889716452620904</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705329</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.403187286894732</v>
+        <v>-5.233322919975653</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4261811060850009</v>
+        <v>0.4941268528526321</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729274</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.511801365338063</v>
+        <v>-5.341936998418984</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5028851354268742</v>
+        <v>0.5708308821945054</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190772</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.598399948319166</v>
+        <v>-5.428535581400087</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.4827587283367558</v>
+        <v>0.5507044751043875</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.560016285761015</v>
+        <v>-5.390151918841936</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.495531634702385</v>
+        <v>0.5634773814700162</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.382899955725849</v>
+        <v>-5.21303558880677</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.5631071955617535</v>
+        <v>0.6310529423293847</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.353197831749555</v>
+        <v>-5.183333464830477</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5756714369141838</v>
+        <v>0.6436171836818154</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7182873419843501</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.173822410510788</v>
+        <v>-5.003958043591709</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6412085807161052</v>
+        <v>0.7091543274837369</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.5615105838136314</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982235</v>
+        <v>3.716991718982234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.218836624031393</v>
+        <v>-5.048972257112315</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6040103506394527</v>
+        <v>0.6719560974070844</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.591859479128236</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.485841134303828</v>
+        <v>-5.31597676738475</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5029001088694245</v>
+        <v>0.5708458556370561</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.7862225171711845</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.587038915741001</v>
+        <v>-5.417174548821922</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.461624918191057</v>
+        <v>0.5295706649586882</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.8546313307165037</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815461</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.554563329570229</v>
+        <v>-5.38469896265115</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4722151142136823</v>
+        <v>0.540160860981314</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.8546313307165037</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.535525201862932</v>
+        <v>-5.365660834943853</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4763550845048461</v>
+        <v>0.5443008312724777</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9128149420476982</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131256</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.56665183301355</v>
+        <v>-5.396787466094471</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6414863009832796</v>
+        <v>0.7094320477509108</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9128149420476982</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.618972213614342</v>
+        <v>-5.449107846695263</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6213914777290963</v>
+        <v>0.689337224496728</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.877868082038826</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.6392295121433</v>
+        <v>-5.469365145224221</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6192970887144389</v>
+        <v>0.6872428354820705</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.877868082038826</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.491486541908297</v>
+        <v>-5.321622174989218</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.757546924600462</v>
+        <v>0.8254926713680937</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7100607248039429</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.593501224439518</v>
+        <v>-5.42363685752044</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7195346731194543</v>
+        <v>0.7874804198870859</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7100607248039429</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.456891880345426</v>
+        <v>-5.287027513426347</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7748407591487498</v>
+        <v>0.8427865059163815</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.5734513807098505</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890616</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.599657213168076</v>
+        <v>-5.429792846248997</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7168151027598002</v>
+        <v>0.7847608495274314</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7162167135325008</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.537359214391953</v>
+        <v>-5.367494847472875</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8080698560670698</v>
+        <v>0.8760156028347015</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7162167135325008</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.335569016726796</v>
+        <v>-5.165704649807717</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5973668075225311</v>
+        <v>0.6653125542901628</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.5181985213633464</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.275678335084202</v>
+        <v>-5.105813968165124</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6916133125017438</v>
+        <v>0.7595590592693751</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.458307839720753</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.373418879709177</v>
+        <v>-5.203554512790098</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6671448307677976</v>
+        <v>0.7350905775354288</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.4741971178537331</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.549756639832106</v>
+        <v>-5.379892272913027</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5951457075432973</v>
+        <v>0.663091454310929</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.6505348779766625</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.549067267670883</v>
+        <v>-5.379202900751804</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5939130744477152</v>
+        <v>0.6618588212153469</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.6505348779766625</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.555638232725475</v>
+        <v>-5.385773865806397</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5911475558613146</v>
+        <v>0.6590933026289458</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.6571058430312555</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863229</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.547684262430703</v>
+        <v>-5.377819895511625</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5943291439792233</v>
+        <v>0.662274890746855</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.6571058430312555</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.537310886097616</v>
+        <v>-5.367446519178538</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6048602515402628</v>
+        <v>0.672805998307894</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.6467324666981682</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326881</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.40962657630332</v>
+        <v>-5.239762209384241</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.660826348832706</v>
+        <v>0.7287720956003376</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5190481569038717</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.470293166705709</v>
+        <v>-5.30042879978663</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6233143851476228</v>
+        <v>0.6912601319152545</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.6007464736224054</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690031</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.405299306772063</v>
+        <v>-5.235434939852984</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6534096317317095</v>
+        <v>0.7213553784993412</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.57391585901825</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674314</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.506057942529061</v>
+        <v>-5.336193575609983</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6172671170599884</v>
+        <v>0.68521286382762</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.6627414277452555</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163224</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.461855105443161</v>
+        <v>-5.291990738524082</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6408278544221857</v>
+        <v>0.7087736011898174</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.618538590659355</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022909</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.498834133106604</v>
+        <v>-5.328969766187525</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6244462438260561</v>
+        <v>0.6923919905936877</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.5815646888680245</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042143</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.518892211971444</v>
+        <v>-5.349027845052365</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6676707774631594</v>
+        <v>0.735616524230791</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.5815646888680245</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.478961538793554</v>
+        <v>-5.309097171874475</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6820837513285687</v>
+        <v>0.7500294980962003</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.5416340156901341</v>
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.464663985310515</v>
+        <v>3.76462218376231</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.858599181891675</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.262668825881008</v>
+        <v>-5.269323065485175</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7531752272255248</v>
+        <v>0.7608873688901907</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.3253413027775883</v>
+        <v>-0.5018599093008336</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.663394400225122</v>
+        <v>2.567857073817508</v>
       </c>
     </row>
   </sheetData>
